--- a/src/attributions/attributions_saliency_traj_394.xlsx
+++ b/src/attributions/attributions_saliency_traj_394.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9.246922854799777e-05</v>
+        <v>0.0001132018151110969</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005129428463988006</v>
+        <v>3.688740980578586e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.039538857294247e-05</v>
+        <v>1.459034501749557e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>9.089522063732147e-05</v>
+        <v>4.636863013729453e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>7.223954889923334e-05</v>
+        <v>1.432893259334378e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005604916368611157</v>
+        <v>0.0001750988885760307</v>
       </c>
       <c r="G4" t="n">
-        <v>2.761170071607921e-05</v>
+        <v>6.845415919087827e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.561921377899125e-05</v>
+        <v>0.0001011006534099579</v>
       </c>
       <c r="I4" t="n">
-        <v>4.53033389931079e-05</v>
+        <v>1.824639730330091e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002141486038453877</v>
+        <v>8.159309072652832e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003697535139508545</v>
+        <v>9.937533468473703e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.811162943951786e-05</v>
+        <v>2.791486440401059e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.785744335502386e-05</v>
+        <v>2.435075111861806e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.595711288857274e-05</v>
+        <v>4.982983591617085e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004005948430858552</v>
+        <v>0.0001835701696109027</v>
       </c>
       <c r="P4" t="n">
-        <v>3.002405719598755e-05</v>
+        <v>0.0001087643395294435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001361130853183568</v>
+        <v>8.703125786269084e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001282274752156809</v>
+        <v>5.404634430306032e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.255107367294841e-05</v>
+        <v>3.651389488368295e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.918580816593021e-05</v>
+        <v>9.981288167182356e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.158120307489298e-05</v>
+        <v>4.853700374951586e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>4.200758849037811e-05</v>
+        <v>6.763265264453366e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001138710285886191</v>
+        <v>0.0001376179570797831</v>
       </c>
       <c r="X4" t="n">
-        <v>4.110363079234958e-05</v>
+        <v>0.0001146462527685799</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.352595351519994e-05</v>
+        <v>3.027890306839254e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.247441079816781e-05</v>
+        <v>1.994767626456451e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.841831155819818e-05</v>
+        <v>4.404220817377791e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.463658403139561e-05</v>
+        <v>1.427992174285464e-06</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.273341674997937e-06</v>
+        <v>1.440991218260024e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.833478669752367e-05</v>
+        <v>3.212266165064648e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0001075915643014014</v>
+        <v>1.218763918586774e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0001318927970714867</v>
+        <v>2.686232619453222e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>8.397256897296757e-05</v>
+        <v>2.812203092616983e-07</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.048416328965686e-05</v>
+        <v>1.575483656779397e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.841603236447554e-05</v>
+        <v>7.4843926995527e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.790867827367038e-05</v>
+        <v>2.515119740564842e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>8.200284355552867e-06</v>
+        <v>1.557075847813394e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.962027090485208e-05</v>
+        <v>2.228768607892562e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.987912663840689e-05</v>
+        <v>2.678016244317405e-06</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.12940639257431e-05</v>
+        <v>5.760495332651772e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.799801222863607e-06</v>
+        <v>7.326226477744058e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0001120428496506065</v>
+        <v>2.010301795962732e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.750134631758556e-05</v>
+        <v>6.794253749831114e-06</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.017768075456843e-05</v>
+        <v>2.987943298649043e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0001431322161806747</v>
+        <v>1.437163064110791e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.942189661960583e-06</v>
+        <v>4.292233825253788e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0001933269377332181</v>
+        <v>0.0001810235989978537</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0001345506170764565</v>
+        <v>1.732694727252237e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.90750504063908e-05</v>
+        <v>1.750387309584767e-05</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.879935295321047e-05</v>
+        <v>1.146643626270816e-06</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001804618514142931</v>
+        <v>0.0001042222211253829</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0001468034461140633</v>
+        <v>5.578889613389038e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.124291394371539e-05</v>
+        <v>7.47024459997192e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0002068414905807003</v>
+        <v>3.883194040099625e-06</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001716115511953831</v>
+        <v>9.106157085625455e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000121854871395044</v>
+        <v>1.878992770798504e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.547608088818379e-05</v>
+        <v>2.098571894748602e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.868685548193753e-05</v>
+        <v>3.318229937576689e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001270179927814752</v>
+        <v>4.518872447079048e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0002584841276984662</v>
+        <v>1.99276164494222e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0001275962713407353</v>
+        <v>2.423653131700121e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.428482396993786e-05</v>
+        <v>0.0001337041176157072</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0001655411761021242</v>
+        <v>2.568439776950981e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.072552731784526e-05</v>
+        <v>2.510085687390529e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.377108416520059e-05</v>
+        <v>6.350944750010967e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.086970405594911e-05</v>
+        <v>3.712036004799302e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.468278034939431e-05</v>
+        <v>3.16015757562127e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.000104457802081015</v>
+        <v>2.907306225097273e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.084369771182537e-05</v>
+        <v>2.113830487360246e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>7.51611078158021e-05</v>
+        <v>3.8015132304281e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.487324516347144e-05</v>
+        <v>5.336101094144396e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.392202340066433e-05</v>
+        <v>2.659983147168532e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.863175516016781e-05</v>
+        <v>2.741729258559644e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0001189485774375498</v>
+        <v>8.09002904134104e-06</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.435079846298322e-05</v>
+        <v>5.51350531168282e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>2.342324296478182e-05</v>
+        <v>0.0001109841687139124</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0001225349988089874</v>
+        <v>0.0001116782223107293</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.023072036332451e-05</v>
+        <v>0.0001371078251395375</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.062085620011203e-06</v>
+        <v>1.210406571772182e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.955210432759486e-06</v>
+        <v>7.849570465623401e-06</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.657408084720373e-05</v>
+        <v>3.001969889737666e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.93087599251885e-06</v>
+        <v>2.01798538910225e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>6.570722325704992e-05</v>
+        <v>1.823577076720539e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>4.619162791641429e-05</v>
+        <v>1.046153192874044e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.145636608474888e-05</v>
+        <v>2.429166852380149e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.511177030508406e-05</v>
+        <v>1.067406810761895e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>9.711701568448916e-05</v>
+        <v>5.246572618489154e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.313238266855478e-05</v>
+        <v>1.263425383513095e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>2.818835127982311e-06</v>
+        <v>1.48760982483509e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>5.638163929688744e-05</v>
+        <v>1.357450582872843e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>4.767029531649314e-05</v>
+        <v>2.605095687613357e-06</v>
       </c>
       <c r="CN4" t="n">
-        <v>9.630175190977752e-05</v>
+        <v>0.0001065958931576461</v>
       </c>
       <c r="CO4" t="n">
-        <v>9.630127169657499e-05</v>
+        <v>1.520705336588435e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.942210893612355e-05</v>
+        <v>4.755299869430019e-06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.728249678009888e-06</v>
+        <v>2.921771920227911e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.707933163037524e-05</v>
+        <v>7.270723290275782e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.142029734386597e-05</v>
+        <v>5.292996866046451e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.490989234298468e-06</v>
+        <v>2.614222648844589e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.000117138224595692</v>
+        <v>1.302330474572955e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.508368768554647e-06</v>
+        <v>2.471845436957665e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>8.463548147119582e-05</v>
+        <v>1.037487709254492e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>3.615337845985778e-05</v>
+        <v>2.005866463150596e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>3.166532405884936e-05</v>
+        <v>2.0234996554791e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>5.366103141568601e-05</v>
+        <v>4.44466968474444e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>9.099396993406117e-05</v>
+        <v>4.073862146469764e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>4.409594112075865e-06</v>
+        <v>1.220738704432733e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>8.693644304003101e-06</v>
+        <v>2.7568603400141e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.954320295131765e-05</v>
+        <v>5.228886948316358e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>5.045710713602602e-05</v>
+        <v>4.625510700861923e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>4.889663978246972e-05</v>
+        <v>5.789525675936602e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>6.161764031276107e-05</v>
+        <v>2.015483005379792e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0001482089282944798</v>
+        <v>7.381521754723508e-06</v>
       </c>
       <c r="DI4" t="n">
-        <v>6.467408093158156e-05</v>
+        <v>2.0180825231364e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002420974196866155</v>
+        <v>3.141683919238858e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0001279058342333883</v>
+        <v>1.643248106120154e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.622539174510166e-05</v>
+        <v>9.134913852903992e-06</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0002304933004779741</v>
+        <v>2.125778337358497e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>4.897782855550759e-05</v>
+        <v>4.381035978440195e-09</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.486541390884668e-05</v>
+        <v>6.984753781580366e-06</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.715833008754998e-05</v>
+        <v>4.417526724864729e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>5.049923856859095e-05</v>
+        <v>6.706044950988144e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.129394023446366e-05</v>
+        <v>4.563157199299894e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>4.575120692607015e-05</v>
+        <v>5.750352283939719e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0001083113893400878</v>
+        <v>3.807922621490434e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>1.802480983315036e-05</v>
+        <v>2.797172783175483e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>4.876899402006529e-05</v>
+        <v>1.548996988276485e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.580260090529919e-05</v>
+        <v>3.588270556065254e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>5.548064291360788e-05</v>
+        <v>2.266195770062041e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.287891740910709e-05</v>
+        <v>3.395120438653976e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.14322634646669e-05</v>
+        <v>1.215534666698659e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>4.665827873395756e-05</v>
+        <v>3.38269819621928e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.864847192540765e-05</v>
+        <v>2.152397973986808e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.50741102010943e-05</v>
+        <v>1.592716944287531e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.239477468421683e-05</v>
+        <v>3.71028327208478e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>5.975672684144229e-05</v>
+        <v>4.284277747501619e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>2.924749787780456e-05</v>
+        <v>3.497015495668165e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>6.724100967403501e-05</v>
+        <v>3.147888855892234e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.638650792301632e-05</v>
+        <v>2.825250157911796e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0001007854152703658</v>
+        <v>2.644647793204058e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>7.757249113637954e-05</v>
+        <v>3.993364953203127e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>4.183825876680203e-05</v>
+        <v>5.020988101023249e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>7.368907245108858e-05</v>
+        <v>3.179138730047271e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>8.491841072100215e-06</v>
+        <v>1.366998503726791e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.12473286309978e-06</v>
+        <v>2.025631874857936e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>5.281010817270726e-05</v>
+        <v>1.349462399957702e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>9.107923688134179e-06</v>
+        <v>9.85437145573087e-06</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.601524854777381e-05</v>
+        <v>5.698854511138052e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.878722418448888e-05</v>
+        <v>2.056956327578519e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001400532491970807</v>
+        <v>2.453292108839378e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001720596919767559</v>
+        <v>7.910526619525626e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>6.733870395692065e-05</v>
+        <v>2.426436185487546e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>4.638644895749167e-05</v>
+        <v>1.791059912648052e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.000114048074465245</v>
+        <v>2.402521431577043e-06</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.977698275368311e-06</v>
+        <v>3.141303386655636e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>8.308819815283641e-05</v>
+        <v>2.01532784558367e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.421216893504607e-05</v>
+        <v>2.531068275857251e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>6.801092240493745e-07</v>
+        <v>2.742461401794571e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>6.494931585621089e-05</v>
+        <v>3.984319846495055e-06</v>
       </c>
       <c r="FC4" t="n">
-        <v>7.260787970153615e-05</v>
+        <v>5.348800186766312e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>4.740640724776313e-05</v>
+        <v>1.146753947978141e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>1.491189959779149e-05</v>
+        <v>1.090245223167585e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>8.745772356633097e-05</v>
+        <v>3.598540843086084e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>4.129721855861135e-05</v>
+        <v>5.607909042737447e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>3.858324635075405e-05</v>
+        <v>2.683771981537575e-06</v>
       </c>
       <c r="FI4" t="n">
-        <v>5.198683356866241e-05</v>
+        <v>1.412725578120444e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0001063227391568944</v>
+        <v>7.954167813295498e-07</v>
       </c>
       <c r="FK4" t="n">
-        <v>5.341502765077166e-05</v>
+        <v>6.438262789743021e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0001052943407557905</v>
+        <v>4.238303517922759e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>3.41292834491469e-05</v>
+        <v>2.779102032945957e-07</v>
       </c>
       <c r="FN4" t="n">
-        <v>5.749497358920053e-05</v>
+        <v>2.390910958638415e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>7.972971070557833e-05</v>
+        <v>2.579411375336349e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.237160828779452e-05</v>
+        <v>7.565639680251479e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0001155772697529756</v>
+        <v>4.767036080011167e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>7.167008880060166e-05</v>
+        <v>3.181844658683985e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>4.887826798949391e-05</v>
+        <v>1.476845409342786e-05</v>
       </c>
       <c r="FT4" t="n">
-        <v>5.473788405652158e-05</v>
+        <v>0.0001832083216868341</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0001926483673742041</v>
+        <v>4.102973980479874e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.562022200436331e-05</v>
+        <v>8.160962170222774e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>4.68872967758216e-05</v>
+        <v>4.316697959438898e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>5.830942973261699e-05</v>
+        <v>3.672312595881522e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>9.290151501772925e-05</v>
+        <v>3.280367309344001e-06</v>
       </c>
       <c r="FZ4" t="n">
-        <v>7.696459215367213e-05</v>
+        <v>6.244791438803077e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>1.40866586662014e-06</v>
+        <v>4.523356619756669e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>5.584630707744509e-05</v>
+        <v>1.510681431682315e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0001282170269405469</v>
+        <v>5.075531953480095e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>6.669949470961001e-06</v>
+        <v>4.258730768924579e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.017476279230323e-05</v>
+        <v>2.134879832738079e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>2.182869866373949e-05</v>
+        <v>3.352382555021904e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>6.711343303322792e-05</v>
+        <v>5.102872364659561e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.055560566484928e-05</v>
+        <v>0.002949364483356476</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01245729345828295</v>
+        <v>0.03625282645225525</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001220989506691694</v>
+        <v>0.002409039530903101</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008292878977954388</v>
+        <v>0.02940476313233376</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008945426903665066</v>
+        <v>0.001536905532702804</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002896663034334779</v>
+        <v>0.007030327804386616</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001491425326094031</v>
+        <v>0.0213540680706501</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007292507798410952</v>
+        <v>0.01807592064142227</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007360816234722733</v>
+        <v>0.01226629689335823</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0007418692111968994</v>
+        <v>0.006243567913770676</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008739110082387924</v>
+        <v>0.03416053950786591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001269258907996118</v>
+        <v>0.009799446910619736</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008061387576162815</v>
+        <v>0.03804883360862732</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01276266947388649</v>
+        <v>0.01185826770961285</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004198492038995028</v>
+        <v>0.01275966688990593</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002883459674194455</v>
+        <v>0.02052012644708157</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0007538581266999245</v>
+        <v>0.007499727886170149</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002017322694882751</v>
+        <v>0.009600322693586349</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002938172838184983</v>
+        <v>0.001386815798468888</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002400405704975128</v>
+        <v>0.004072407260537148</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001702066045254469</v>
+        <v>0.001969080651178956</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0002059307007584721</v>
+        <v>0.0001708837226033211</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001011634478345513</v>
+        <v>0.00289693265222013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003080850001424551</v>
+        <v>0.007756962906569242</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001938978326506913</v>
+        <v>0.002544865477830172</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002129581058397889</v>
+        <v>0.01499199122190475</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0007478160550817847</v>
+        <v>0.00259292358532548</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002428744221106172</v>
+        <v>0.0004507285775616765</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002472685417160392</v>
+        <v>0.003557596821337938</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001211612718179822</v>
+        <v>0.003806019900366664</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001430775388143957</v>
+        <v>0.002223853953182697</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003943496383726597</v>
+        <v>0.002321336884051561</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001420885906554759</v>
+        <v>0.01855354011058807</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0001575421774759889</v>
+        <v>0.001823192345909774</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003240900114178658</v>
+        <v>0.0112820090726018</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002361680846661329</v>
+        <v>0.002768088364973664</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0004041078209411353</v>
+        <v>0.00172735087107867</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0006239832146093249</v>
+        <v>0.006744625046849251</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0004707266925834119</v>
+        <v>0.006277692038565874</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0004743488098029047</v>
+        <v>0.00367372389882803</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.003909468185156584</v>
+        <v>0.004714329726994038</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.002183291595429182</v>
+        <v>0.00424018781632185</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0002241492038592696</v>
+        <v>0.005839305929839611</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0002630559611134231</v>
+        <v>0.0007084915414452553</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0003448436327744275</v>
+        <v>0.00140565144829452</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0004569784214254469</v>
+        <v>0.001317801070399582</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.009379666298627853</v>
+        <v>0.01142569072544575</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0005788596463389695</v>
+        <v>0.004184070974588394</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001067865057848394</v>
+        <v>0.014260059222579</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001451173913665116</v>
+        <v>0.02787197381258011</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001274475362151861</v>
+        <v>0.01039964891970158</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001111879479140043</v>
+        <v>0.0007000929908826947</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.001097045140340924</v>
+        <v>0.001497665653005242</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.00359094375744462</v>
+        <v>0.004520478658378124</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.001402063295245171</v>
+        <v>0.007214312441647053</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003531210590153933</v>
+        <v>0.007073886692523956</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003125334391370416</v>
+        <v>0.006655249278992414</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.003231109818443656</v>
+        <v>0.003675768850371242</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.008141480386257172</v>
+        <v>0.01555898226797581</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0054027303121984</v>
+        <v>0.002157265786081553</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002727500395849347</v>
+        <v>0.006729893386363983</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0009279778460040689</v>
+        <v>0.02256102114915848</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.002504704054445028</v>
+        <v>0.002021847292780876</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002027989365160465</v>
+        <v>0.0003620952775236219</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.004300299100577831</v>
+        <v>0.005001108627766371</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001729003619402647</v>
+        <v>0.004257518332451582</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001487222849391401</v>
+        <v>0.006222846917808056</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.004711566027253866</v>
+        <v>0.008322093635797501</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002995804883539677</v>
+        <v>0.002359093865379691</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001272344030439854</v>
+        <v>0.002303567714989185</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.002256474224850535</v>
+        <v>0.006034122779965401</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001362327486276627</v>
+        <v>0.004825773648917675</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0003056966525036842</v>
+        <v>0.001118446234613657</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.003860594006255269</v>
+        <v>0.01039007119834423</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001412715879268944</v>
+        <v>0.006583601236343384</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0005890537286177278</v>
+        <v>0.01904007792472839</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0007310699438676238</v>
+        <v>0.001283661928027868</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.002037058118730783</v>
+        <v>0.006694411393254995</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0004580709501169622</v>
+        <v>0.003841831814497709</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.001100584398955107</v>
+        <v>0.004529943224042654</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.00154351897072047</v>
+        <v>0.0009015050600282848</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.947484169155359e-06</v>
+        <v>0.00106954830698669</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.002247737487778068</v>
+        <v>0.009558207355439663</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.000309889845084399</v>
+        <v>0.000178435118868947</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0008242276962846518</v>
+        <v>0.01216613315045834</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0005845560226589441</v>
+        <v>0.001613129395991564</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0005491084884852171</v>
+        <v>0.0009370440384373069</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0006567650707438588</v>
+        <v>0.0006653829477727413</v>
       </c>
       <c r="CK5" t="n">
-        <v>7.987837307155132e-05</v>
+        <v>0.0005731911514885724</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001622008625417948</v>
+        <v>0.00198426959104836</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.002978431526571512</v>
+        <v>0.003322009928524494</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.00244265585206449</v>
+        <v>0.0004575280472636223</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001220598933286965</v>
+        <v>0.01807334832847118</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.002783283125609159</v>
+        <v>0.02166534215211868</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002922951942309737</v>
+        <v>0.001120293629355729</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0005124637391418219</v>
+        <v>0.007612855173647404</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.017641423270106e-05</v>
+        <v>0.01144307479262352</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001891442574560642</v>
+        <v>0.008482598699629307</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0003862616431433707</v>
+        <v>0.00302414339967072</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001930290454765782</v>
+        <v>0.0009587837266735733</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001587537582963705</v>
+        <v>0.009459316730499268</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.001082536648027599</v>
+        <v>0.001303117955103517</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0009056541603058577</v>
+        <v>0.01275713555514812</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0005037912633270025</v>
+        <v>0.0003960140747949481</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001355220883851871</v>
+        <v>0.001413418678566813</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.000520884757861495</v>
+        <v>0.0001614473294466734</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004144118574913591</v>
+        <v>0.001582802156917751</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0009012646041810513</v>
+        <v>0.000219162495341152</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.00125537347048521</v>
+        <v>0.002047902438789606</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.00324317323975265</v>
+        <v>0.009846850298345089</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002798681613057852</v>
+        <v>0.005143151152879</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.005507495254278183</v>
+        <v>0.0142123457044363</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002213569125160575</v>
+        <v>0.005718853790313005</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001729775569401681</v>
+        <v>0.01205341890454292</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.52320644701831e-05</v>
+        <v>0.003564342390745878</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001707124756649137</v>
+        <v>0.01645173132419586</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001390683028148487</v>
+        <v>0.00166554341558367</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001020189258269966</v>
+        <v>0.001689771423116326</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0009530297829769552</v>
+        <v>0.005612031556665897</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001535907387733459</v>
+        <v>0.0008689931128174067</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.000256810977589339</v>
+        <v>0.008398831821978092</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0006818841793574393</v>
+        <v>0.002650911221280694</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.000250641256570816</v>
+        <v>0.003165628761053085</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001420132583007216</v>
+        <v>0.007130592130124569</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0008584968745708466</v>
+        <v>0.004577620420604944</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.002254118211567402</v>
+        <v>0.01697254367172718</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0005146481562405825</v>
+        <v>7.687737524975091e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001522525446489453</v>
+        <v>0.00557594234123826</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0001671138743404299</v>
+        <v>0.003993256483227015</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0009817917598411441</v>
+        <v>0.0004575393395498395</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001327356905676425</v>
+        <v>0.004833418410271406</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003174444660544395</v>
+        <v>0.004794429987668991</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0008509597973898053</v>
+        <v>0.002532336162403226</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001219378318637609</v>
+        <v>0.01699529774487019</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0006379772676154971</v>
+        <v>0.01368480082601309</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0006258385255932808</v>
+        <v>0.006072116084396839</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001369616948068142</v>
+        <v>0.007210426032543182</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002647366491146386</v>
+        <v>0.005315361078828573</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.002013360382989049</v>
+        <v>0.01311307679861784</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.002745352918282151</v>
+        <v>0.003738732542842627</v>
       </c>
       <c r="EK5" t="n">
-        <v>9.132814011536539e-05</v>
+        <v>0.000344631407642737</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001883732387796044</v>
+        <v>0.001044641714543104</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0004052598378621042</v>
+        <v>0.003789460752159357</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001199179911054671</v>
+        <v>0.001096886466257274</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001054749125614762</v>
+        <v>0.001499469857662916</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002151981228962541</v>
+        <v>0.01374008506536484</v>
       </c>
       <c r="EQ5" t="n">
-        <v>6.901253073010594e-05</v>
+        <v>0.0005716364830732346</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002176955458708107</v>
+        <v>0.007494300603866577</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0006338111124932766</v>
+        <v>0.0009375428780913353</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001128148986026645</v>
+        <v>0.005086249671876431</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0003908953221980482</v>
+        <v>0.005068862810730934</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.001180498977191746</v>
+        <v>0.0008543249568901956</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0007133028702810407</v>
+        <v>0.004578561056405306</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0004976978525519371</v>
+        <v>0.00075749889947474</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.00188751460518688</v>
+        <v>0.00948223564773798</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001641440176172182</v>
+        <v>0.0008184891194105148</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001041324576362967</v>
+        <v>0.01561443973332644</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.001243845792487264</v>
+        <v>5.547761247726157e-05</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.001141910324804485</v>
+        <v>0.001523587037809193</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0002727164828684181</v>
+        <v>0.0009172023856081069</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0002339797792956233</v>
+        <v>0.0004850412369705737</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0007193755591288209</v>
+        <v>0.001178142847493291</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0008315028971992433</v>
+        <v>0.004435759969055653</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001857610768638551</v>
+        <v>0.005144087132066488</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0009771321201696992</v>
+        <v>0.002035385929048061</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001860148971900344</v>
+        <v>0.01050704531371593</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001213328680023551</v>
+        <v>0.003753329394385219</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.002273577265441418</v>
+        <v>0.001735976082272828</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0006682469975203276</v>
+        <v>0.001120595959946513</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0006008744239807129</v>
+        <v>0.003327627666294575</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001917330082505941</v>
+        <v>0.001868712017312646</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001411806792020798</v>
+        <v>0.007851246744394302</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0007345368503592908</v>
+        <v>0.01120849046856165</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001992592820897698</v>
+        <v>0.001117317005991936</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.00131842982955277</v>
+        <v>0.006372891832143068</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002714599017053843</v>
+        <v>0.01462266780436039</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00172676844522357</v>
+        <v>0.01340220682322979</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0003842742298729718</v>
+        <v>0.005496310535818338</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002946984488517046</v>
+        <v>0.004334663972258568</v>
       </c>
       <c r="FX5" t="n">
-        <v>6.89135049469769e-05</v>
+        <v>0.01433019153773785</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001730432035401464</v>
+        <v>0.00352940009906888</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001480071106925607</v>
+        <v>0.001302236458286643</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.00106829940341413</v>
+        <v>0.005318508017808199</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.00122772459872067</v>
+        <v>0.01473896950483322</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.00308210588991642</v>
+        <v>0.001239914330653846</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001991811441257596</v>
+        <v>0.003672069869935513</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0002729058032855392</v>
+        <v>0.007032477296888828</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001338451635092497</v>
+        <v>0.001476571778766811</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002122879028320312</v>
+        <v>0.001743350643664598</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0002976151299662888</v>
+        <v>1.058206473836254e-12</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0005746367387473583</v>
+        <v>2.861158358846705e-12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001906819234136492</v>
+        <v>9.482342211777905e-13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001099547880585305</v>
+        <v>3.518707677660493e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001888366648927331</v>
+        <v>1.916537024568288e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001299515832215548</v>
+        <v>4.656923718177053e-12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007546003325842321</v>
+        <v>3.719007306973721e-12</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005084879812784493</v>
+        <v>7.819475102144313e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001367022516205907</v>
+        <v>4.590188092904596e-14</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003204047388862818</v>
+        <v>1.438616803808856e-12</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002452114422339946</v>
+        <v>1.059622008192651e-12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002856759238056839</v>
+        <v>2.129722179861071e-12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002758329210337251</v>
+        <v>1.267568949109288e-12</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002120947930961847</v>
+        <v>3.970497108179982e-12</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001163528067991138</v>
+        <v>5.233046201230662e-12</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001940242946147919</v>
+        <v>6.387009410940836e-12</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.695311897899956e-05</v>
+        <v>7.189596140655397e-12</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003396034881006926</v>
+        <v>1.025819511800419e-12</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003090451064053923</v>
+        <v>5.246359444967263e-13</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004091092268936336</v>
+        <v>2.222753448313797e-12</v>
       </c>
       <c r="U6" t="n">
-        <v>3.876708797179163e-05</v>
+        <v>1.288565066280556e-13</v>
       </c>
       <c r="V6" t="n">
-        <v>7.540715159848332e-05</v>
+        <v>1.07774390540466e-12</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0006168023683130741</v>
+        <v>4.100207152968327e-12</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005146913463249803</v>
+        <v>3.831843560985967e-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0003301674732938409</v>
+        <v>1.469498784809065e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002102536091115326</v>
+        <v>4.651668373406581e-12</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0005899441312067211</v>
+        <v>2.535593805232106e-13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00015228871779982</v>
+        <v>1.24489459539523e-12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001136060571298003</v>
+        <v>1.317876797274353e-12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0006472382228821516</v>
+        <v>1.753536552073776e-13</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0002632357063703239</v>
+        <v>1.51725637262401e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001646353281103075</v>
+        <v>1.610356379494471e-12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001349998055957258</v>
+        <v>3.107852733844063e-12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001035170396789908</v>
+        <v>1.036366196853489e-12</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0004780310264322907</v>
+        <v>1.82884480129375e-12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0009264568798243999</v>
+        <v>2.622398283767813e-13</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0001678272383287549</v>
+        <v>3.283795219251318e-13</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0003614220477174968</v>
+        <v>6.635935290849604e-13</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.570269084069878e-06</v>
+        <v>2.835286801346204e-13</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0008925211732275784</v>
+        <v>4.949727693687178e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0004728900676127523</v>
+        <v>1.83772268236293e-12</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001602489501237869</v>
+        <v>5.871520717543044e-13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0007263484294526279</v>
+        <v>1.001795434801833e-12</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0004669951158575714</v>
+        <v>1.430690635406684e-12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0002168635110137984</v>
+        <v>7.955029321903007e-13</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0003855961840599775</v>
+        <v>1.770499979264484e-13</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0008680497412569821</v>
+        <v>4.008411224470931e-12</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.850613423623145e-05</v>
+        <v>2.275375200755381e-12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0004782069299835712</v>
+        <v>1.913603824010845e-12</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0012400031555444</v>
+        <v>1.948606857468671e-12</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0008313592406921089</v>
+        <v>5.249752021985188e-12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001880844589322805</v>
+        <v>9.661805860580741e-13</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0008772944565862417</v>
+        <v>2.859814164993257e-12</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0005677307490259409</v>
+        <v>2.040221832623479e-14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0007932055741548538</v>
+        <v>1.154484168854053e-12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0003834654635284096</v>
+        <v>3.737333793135678e-12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0002355542383156717</v>
+        <v>6.498134821029955e-13</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0002877889783121645</v>
+        <v>1.667950716779942e-12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001762003870680928</v>
+        <v>1.037314982174631e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001191435614600778</v>
+        <v>2.272019378191104e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0005209441296756268</v>
+        <v>4.491998949456705e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0005235875141806901</v>
+        <v>6.238036129313507e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0008717706659808755</v>
+        <v>7.507216961792629e-13</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0001512771414127201</v>
+        <v>1.413872708147523e-12</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0007135850028134882</v>
+        <v>7.379315799908859e-13</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0003265381092205644</v>
+        <v>5.946882526350339e-13</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0009684000397101045</v>
+        <v>4.12205697093021e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0001392773556290194</v>
+        <v>1.478233117510608e-12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0003027218044735491</v>
+        <v>7.5464021967106e-13</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0009054234251379967</v>
+        <v>5.374979974992478e-13</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.1745111704804e-05</v>
+        <v>2.97395192239841e-13</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0006132049020379782</v>
+        <v>9.999212829264748e-13</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0003113253624178469</v>
+        <v>2.36876490644633e-13</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0003476714482530951</v>
+        <v>3.63925171465232e-13</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0004756515845656395</v>
+        <v>7.542051835493502e-14</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0002830760204233229</v>
+        <v>3.142322773513895e-12</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007149639423005283</v>
+        <v>2.80277645710314e-12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.375652886461467e-05</v>
+        <v>7.559032067817884e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0004369956732261926</v>
+        <v>1.187892015655501e-13</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0004173428169451654</v>
+        <v>1.412330755817814e-12</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.000374875933630392</v>
+        <v>4.613868423604395e-14</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.786208617384546e-05</v>
+        <v>5.303526715016993e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>9.350557229481637e-05</v>
+        <v>4.812358194231092e-13</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0001592571788933128</v>
+        <v>2.670586191425017e-13</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0002960542333312333</v>
+        <v>2.301448690910507e-13</v>
       </c>
       <c r="CH6" t="n">
-        <v>4.188948514638469e-05</v>
+        <v>1.560898220571982e-13</v>
       </c>
       <c r="CI6" t="n">
-        <v>5.196303391130641e-06</v>
+        <v>9.116890185498217e-13</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0002194338303525001</v>
+        <v>3.710610106937712e-13</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001823222846724093</v>
+        <v>4.132254434463523e-13</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0003478191792964935</v>
+        <v>1.24724742252974e-12</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0002422091492917389</v>
+        <v>1.680730858308332e-12</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0003235296462662518</v>
+        <v>1.449164573064099e-12</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0001746674097375944</v>
+        <v>1.387277879377757e-12</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0008564871968701482</v>
+        <v>1.769536557214013e-12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0008477982482872903</v>
+        <v>8.269795438720084e-13</v>
       </c>
       <c r="CR6" t="n">
-        <v>2.767934347502887e-05</v>
+        <v>1.862946212224936e-12</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0003439534339122474</v>
+        <v>3.881837993408022e-12</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0003090826794505119</v>
+        <v>1.625823932947801e-12</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.001649460289627314</v>
+        <v>2.723620374373015e-12</v>
       </c>
       <c r="CV6" t="n">
-        <v>7.411596016027033e-06</v>
+        <v>3.90739442754709e-13</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.889905252028257e-05</v>
+        <v>2.870590050385591e-13</v>
       </c>
       <c r="CX6" t="n">
-        <v>4.944951797369868e-05</v>
+        <v>3.360913977679125e-13</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0002453418273944408</v>
+        <v>2.037366044101152e-13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0001748710637912154</v>
+        <v>1.043747662084205e-12</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0002078295656247064</v>
+        <v>1.276249830643728e-12</v>
       </c>
       <c r="DB6" t="n">
-        <v>5.924209835939109e-05</v>
+        <v>7.504368762685509e-13</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0001010646228678524</v>
+        <v>3.800897856003072e-13</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0003021777956746519</v>
+        <v>1.141884438567164e-12</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0002280081534991041</v>
+        <v>3.288933795447813e-12</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0006913333781994879</v>
+        <v>4.437525867595493e-12</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001729084906401113</v>
+        <v>2.136853628070812e-12</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0007721353322267532</v>
+        <v>2.421896667589851e-12</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0003272672765888274</v>
+        <v>6.697678436168308e-13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001948886085301638</v>
+        <v>5.561215984245527e-12</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0007910066051408648</v>
+        <v>4.453608163680622e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0002027653390541673</v>
+        <v>2.406453942366271e-12</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.001400592853315175</v>
+        <v>3.768066587916952e-13</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0002838855725713074</v>
+        <v>2.616171602271011e-12</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001463837834307924</v>
+        <v>2.645343254344124e-13</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0003490013768896461</v>
+        <v>3.557401768994328e-13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>4.248693585395813e-06</v>
+        <v>4.185305314124976e-12</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001133216428570449</v>
+        <v>2.828526475540105e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0006572924321517348</v>
+        <v>1.531624436654222e-12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.001055702683515847</v>
+        <v>2.053638292406901e-12</v>
       </c>
       <c r="DU6" t="n">
-        <v>5.077142850495875e-05</v>
+        <v>1.318467579038141e-12</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.001278077252209187</v>
+        <v>1.820711685801904e-13</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0003352920757606626</v>
+        <v>9.513082595974387e-13</v>
       </c>
       <c r="DX6" t="n">
-        <v>8.284479554276913e-05</v>
+        <v>1.481808165754162e-12</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0001958848006324843</v>
+        <v>1.705670110360713e-12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0007557244971394539</v>
+        <v>2.165765830564048e-12</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0003387375909369439</v>
+        <v>2.558524139079088e-12</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001873133733170107</v>
+        <v>1.919471743008772e-12</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.895058762282133e-05</v>
+        <v>1.258147665911258e-12</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0005664126947522163</v>
+        <v>6.279299454535481e-13</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001798053563106805</v>
+        <v>5.337393938278923e-13</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0001751220115693286</v>
+        <v>2.413209606103028e-13</v>
       </c>
       <c r="EG6" t="n">
-        <v>6.012346420902759e-05</v>
+        <v>3.730743199179681e-13</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001379643217660487</v>
+        <v>1.20729533141517e-12</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.001548282103613019</v>
+        <v>1.656044550622793e-12</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0002357445482630283</v>
+        <v>1.915808874389247e-12</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.001215080264955759</v>
+        <v>1.110799928601136e-12</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0008420778322033584</v>
+        <v>3.862624196188102e-13</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0002256151637993753</v>
+        <v>4.060949710185668e-13</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002314373559784144</v>
+        <v>1.524414709047628e-12</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0003605030942708254</v>
+        <v>7.456506115680051e-13</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0002091498608933762</v>
+        <v>1.851187605983462e-12</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001612366177141666</v>
+        <v>2.290988037299824e-13</v>
       </c>
       <c r="ER6" t="n">
-        <v>4.884417649009265e-05</v>
+        <v>5.644582566112499e-13</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0002245237701572478</v>
+        <v>2.079112923492055e-12</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0006137855816632509</v>
+        <v>5.584456508334057e-13</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0005514385993592441</v>
+        <v>8.624904718375348e-13</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.154752681031823e-06</v>
+        <v>2.359332347545706e-14</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0003054145199712366</v>
+        <v>3.180163380897549e-13</v>
       </c>
       <c r="EX6" t="n">
-        <v>5.780094579677097e-05</v>
+        <v>4.960371306414468e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>3.101269976468757e-05</v>
+        <v>2.983765849413206e-13</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001550930028315634</v>
+        <v>1.777153592471756e-13</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0004350353265181184</v>
+        <v>2.625248109178191e-13</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0001233098155353218</v>
+        <v>8.497476268638782e-13</v>
       </c>
       <c r="FC6" t="n">
-        <v>3.31941555486992e-06</v>
+        <v>1.198741193114694e-12</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0002011648612096906</v>
+        <v>5.260776623355889e-13</v>
       </c>
       <c r="FE6" t="n">
-        <v>9.051879897015169e-05</v>
+        <v>5.13135757843064e-13</v>
       </c>
       <c r="FF6" t="n">
-        <v>8.710481051821262e-05</v>
+        <v>1.02560668291396e-12</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0001601568510523066</v>
+        <v>3.155471760621364e-12</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0003173571894876659</v>
+        <v>1.086581562573241e-12</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0002909400791395456</v>
+        <v>1.180751351727294e-12</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.001017192029394209</v>
+        <v>5.082263277757237e-13</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0006290187011472881</v>
+        <v>9.504441504659678e-15</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0003839959972538054</v>
+        <v>1.717298395501055e-12</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003948241646867245</v>
+        <v>5.422008870527295e-13</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0003710497985593975</v>
+        <v>3.515125040001732e-12</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0007121621747501194</v>
+        <v>2.123865970246608e-12</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0008707286324352026</v>
+        <v>1.166932869778314e-12</v>
       </c>
       <c r="FQ6" t="n">
-        <v>7.912448199931532e-05</v>
+        <v>3.139339265975649e-12</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0006615507300011814</v>
+        <v>4.156376198077849e-12</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0001302513264818117</v>
+        <v>7.509484570636382e-13</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001003778539597988</v>
+        <v>1.072188345052627e-12</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001688823336735368</v>
+        <v>1.609278709640075e-13</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0004544557305052876</v>
+        <v>4.618099739422954e-12</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0005934230284765363</v>
+        <v>3.03709097801419e-12</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0001982552785193548</v>
+        <v>1.436582298432187e-12</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0004104207037016749</v>
+        <v>4.963965978717344e-13</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.000406199018470943</v>
+        <v>2.301183874529877e-13</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0003250422305427492</v>
+        <v>1.089697125936095e-12</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0003165534872096032</v>
+        <v>3.630714977796712e-13</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0006465361802838743</v>
+        <v>2.417897045775552e-12</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0001935186301125214</v>
+        <v>1.363895433224849e-12</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.001271159620955586</v>
+        <v>2.283658762851186e-14</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0008782495278865099</v>
+        <v>2.549834475507051e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001761976862326264</v>
+        <v>4.153138878811025e-13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.233742689763176e-09</v>
+        <v>3.671533131300729e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>1.323337661673918e-09</v>
+        <v>5.394281678985729e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>4.034126366292412e-09</v>
+        <v>2.291855161868587e-15</v>
       </c>
       <c r="D7" t="n">
-        <v>9.830027902779648e-10</v>
+        <v>1.681118148876871e-15</v>
       </c>
       <c r="E7" t="n">
-        <v>2.328070625168266e-09</v>
+        <v>9.146093416653668e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>3.537066861625249e-09</v>
+        <v>5.055393749426413e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>7.602940499396027e-09</v>
+        <v>4.446521691226315e-16</v>
       </c>
       <c r="H7" t="n">
-        <v>1.273747107788381e-09</v>
+        <v>6.632549615456134e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.394643150438469e-09</v>
+        <v>4.108190262313346e-15</v>
       </c>
       <c r="J7" t="n">
-        <v>1.17220366746551e-09</v>
+        <v>2.48617669606734e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>5.539550151922867e-09</v>
+        <v>4.600078811926389e-15</v>
       </c>
       <c r="L7" t="n">
-        <v>5.041419726126151e-09</v>
+        <v>2.016800482247303e-15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05116110155268e-09</v>
+        <v>3.78945726997571e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.507727276361948e-08</v>
+        <v>2.050885273333273e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>5.839938532758993e-10</v>
+        <v>4.584451901082495e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721042058340117e-09</v>
+        <v>1.588457297249342e-15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.78241232673804e-09</v>
+        <v>1.658250271004255e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>6.308110478414619e-09</v>
+        <v>2.768613797219537e-15</v>
       </c>
       <c r="S7" t="n">
-        <v>5.34428390430719e-10</v>
+        <v>1.117473944291009e-15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.676719874055266e-10</v>
+        <v>2.415656015131618e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>9.629170794056563e-10</v>
+        <v>1.306615766138183e-15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.522530324038485e-09</v>
+        <v>2.638511018828935e-15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.220349932218312e-09</v>
+        <v>4.961793220623024e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>6.308067845850474e-09</v>
+        <v>2.189264648879514e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.137483606252545e-09</v>
+        <v>8.179501768894423e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.924330694791365e-09</v>
+        <v>1.178757519178686e-15</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.816686966473526e-10</v>
+        <v>8.587104611025033e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.225227224705861e-10</v>
+        <v>1.383174839075763e-15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.02887243169647e-09</v>
+        <v>7.961438959975316e-16</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.183304369576035e-09</v>
+        <v>1.314949935064455e-15</v>
       </c>
       <c r="AE7" t="n">
-        <v>6.686795561705594e-09</v>
+        <v>2.775737556064183e-15</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.724036773926741e-09</v>
+        <v>2.085642079183771e-16</v>
       </c>
       <c r="AG7" t="n">
-        <v>8.990144184650717e-10</v>
+        <v>1.729752133730253e-15</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.047893632450837e-09</v>
+        <v>8.744484391416067e-16</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.812976518384858e-09</v>
+        <v>2.48581914228448e-15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.141958249130994e-09</v>
+        <v>5.460193547776322e-16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.815701589080732e-09</v>
+        <v>1.287415858564533e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.551813648223657e-10</v>
+        <v>1.278396545863051e-15</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.749428155787939e-10</v>
+        <v>7.056407019844554e-16</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.359299866583342e-09</v>
+        <v>3.004485579733785e-15</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.234340072490795e-09</v>
+        <v>1.706188841807941e-15</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.584719993592444e-09</v>
+        <v>2.236748521809202e-16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.45924217154203e-09</v>
+        <v>2.068913443173295e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.08894945785687e-09</v>
+        <v>8.253658974030945e-16</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.039094697067981e-10</v>
+        <v>8.815899856781445e-16</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.033387597715318e-09</v>
+        <v>5.142326434869017e-17</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.547417801845313e-09</v>
+        <v>6.328679933760442e-15</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.146033934418256e-09</v>
+        <v>1.063007502321071e-15</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.534930374613168e-10</v>
+        <v>1.434782544848718e-15</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.360840440334243e-09</v>
+        <v>1.03632998788906e-15</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.808509394635621e-09</v>
+        <v>9.04837254901792e-17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.537021954156614e-09</v>
+        <v>6.842374499567601e-16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.164540464060337e-09</v>
+        <v>1.719721675447986e-15</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.846548495862635e-09</v>
+        <v>1.162512274283296e-15</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.562679846107585e-09</v>
+        <v>1.210166242016704e-15</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.098577116058323e-10</v>
+        <v>1.386654873939558e-15</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.895677919667605e-09</v>
+        <v>6.375891220899792e-16</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.511981372383843e-09</v>
+        <v>1.94901984701683e-15</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.796150309185123e-09</v>
+        <v>1.072345722927194e-15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.518827451642892e-10</v>
+        <v>2.612113025269517e-15</v>
       </c>
       <c r="BI7" t="n">
-        <v>7.2254252581061e-10</v>
+        <v>1.464688948875663e-15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.770642521492505e-10</v>
+        <v>1.916392561405068e-15</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.717212398475112e-09</v>
+        <v>1.296655823348775e-15</v>
       </c>
       <c r="BL7" t="n">
-        <v>8.203014378871387e-10</v>
+        <v>2.055719316833033e-15</v>
       </c>
       <c r="BM7" t="n">
-        <v>6.722701062500391e-09</v>
+        <v>1.859148804280201e-15</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.469022457127437e-11</v>
+        <v>1.931571815336338e-16</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.381922132281943e-09</v>
+        <v>4.616165449902406e-16</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.468017973849101e-08</v>
+        <v>2.441306078598609e-15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.479420307428427e-09</v>
+        <v>1.872166641888316e-15</v>
       </c>
       <c r="BR7" t="n">
-        <v>4.533457609312563e-09</v>
+        <v>2.78961915552026e-15</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.786339573101486e-09</v>
+        <v>3.23000291386344e-16</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.710212220260246e-10</v>
+        <v>4.883080354658813e-16</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.145892047915709e-09</v>
+        <v>3.457098270373831e-16</v>
       </c>
       <c r="BV7" t="n">
-        <v>3.462029773970698e-09</v>
+        <v>1.048525780021864e-15</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.21057408541958e-09</v>
+        <v>1.967731863612861e-15</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.325383885448673e-09</v>
+        <v>3.209303863852269e-15</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.949598064740712e-09</v>
+        <v>2.862414861073189e-15</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.763267836769501e-09</v>
+        <v>2.778788145223719e-15</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.161757078373739e-09</v>
+        <v>3.511631839704839e-16</v>
       </c>
       <c r="CB7" t="n">
-        <v>9.00783114765602e-10</v>
+        <v>2.035261353574474e-15</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.023574723926004e-09</v>
+        <v>2.341362331811469e-15</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.145085468782895e-10</v>
+        <v>7.920374802692428e-16</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.448481778965061e-09</v>
+        <v>8.92904545908449e-17</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.187064418457396e-10</v>
+        <v>2.924371191879223e-16</v>
       </c>
       <c r="CG7" t="n">
-        <v>8.93597751350228e-10</v>
+        <v>9.860431241182294e-16</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.211458711125601e-11</v>
+        <v>1.567013202351722e-16</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.435350727163609e-09</v>
+        <v>9.237749793084872e-16</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.854976172666056e-09</v>
+        <v>4.111603805090781e-16</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.240538338720398e-09</v>
+        <v>4.739466977243031e-16</v>
       </c>
       <c r="CL7" t="n">
-        <v>9.634086861609603e-10</v>
+        <v>1.13018028553277e-15</v>
       </c>
       <c r="CM7" t="n">
-        <v>3.031772166650626e-09</v>
+        <v>5.948415927035412e-16</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.119895257228336e-09</v>
+        <v>3.074290835466433e-15</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.293098073062993e-09</v>
+        <v>1.057032214273783e-15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.764855039887436e-09</v>
+        <v>6.129301930503936e-16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>9.946726997611677e-09</v>
+        <v>1.463497597035349e-15</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.723181819457409e-09</v>
+        <v>3.270223743968219e-16</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.43524711507348e-09</v>
+        <v>6.173789159684916e-16</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.63404817349533e-09</v>
+        <v>6.444106489911325e-16</v>
       </c>
       <c r="CU7" t="n">
-        <v>2.555550659977257e-09</v>
+        <v>1.363025089930886e-15</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.049791405003056e-11</v>
+        <v>1.003438427997754e-15</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.427878260074067e-09</v>
+        <v>1.305436061000895e-16</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.589829934367515e-10</v>
+        <v>1.860575366582055e-16</v>
       </c>
       <c r="CY7" t="n">
-        <v>6.506886141011137e-10</v>
+        <v>1.20639313375316e-15</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.788186348468003e-10</v>
+        <v>3.369544180385298e-16</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.336476151969634e-09</v>
+        <v>8.537994170138821e-16</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.053919923028502e-09</v>
+        <v>1.98272651730119e-16</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.109997649351158e-09</v>
+        <v>2.446810839843697e-16</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.195247234520025e-10</v>
+        <v>9.788122156057563e-16</v>
       </c>
       <c r="DE7" t="n">
-        <v>7.281530045588624e-09</v>
+        <v>6.340734059632818e-16</v>
       </c>
       <c r="DF7" t="n">
-        <v>6.536894137099125e-09</v>
+        <v>1.233824719266464e-15</v>
       </c>
       <c r="DG7" t="n">
-        <v>5.169991101894311e-10</v>
+        <v>1.808726838754284e-15</v>
       </c>
       <c r="DH7" t="n">
-        <v>8.485848468353652e-09</v>
+        <v>7.662833905684166e-16</v>
       </c>
       <c r="DI7" t="n">
-        <v>1.037554042682132e-08</v>
+        <v>4.08233775797196e-16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.784661917194398e-09</v>
+        <v>1.800872090476158e-15</v>
       </c>
       <c r="DK7" t="n">
-        <v>7.64747731807347e-09</v>
+        <v>5.550575139621908e-16</v>
       </c>
       <c r="DL7" t="n">
-        <v>6.730707990953988e-09</v>
+        <v>1.128547100131346e-15</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.030903889504998e-09</v>
+        <v>2.930990754362016e-16</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.176677644210145e-09</v>
+        <v>6.261792706531086e-16</v>
       </c>
       <c r="DO7" t="n">
-        <v>6.768051674654885e-10</v>
+        <v>3.948292147091007e-16</v>
       </c>
       <c r="DP7" t="n">
-        <v>2.194062709293121e-09</v>
+        <v>4.611246306061227e-16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.460660037366779e-09</v>
+        <v>2.872935857311035e-15</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.850449876135031e-09</v>
+        <v>9.900246024867982e-16</v>
       </c>
       <c r="DS7" t="n">
-        <v>6.909656180553725e-11</v>
+        <v>2.095486666673675e-15</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.897938055137274e-09</v>
+        <v>1.440539616032969e-15</v>
       </c>
       <c r="DU7" t="n">
-        <v>3.391964487065025e-09</v>
+        <v>7.879769631387833e-16</v>
       </c>
       <c r="DV7" t="n">
-        <v>4.714156287555227e-10</v>
+        <v>2.86863377697193e-16</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.340425075963992e-10</v>
+        <v>1.140523934247285e-15</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.33365363197413e-09</v>
+        <v>5.097879439753031e-16</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.692553652787865e-09</v>
+        <v>3.773718921359692e-16</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.778160146377218e-09</v>
+        <v>1.162876710208852e-15</v>
       </c>
       <c r="EA7" t="n">
-        <v>7.37729877187121e-10</v>
+        <v>1.286816423935673e-16</v>
       </c>
       <c r="EB7" t="n">
-        <v>9.511781362547822e-10</v>
+        <v>5.878698233333687e-16</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.083039074562976e-09</v>
+        <v>1.586974777833411e-15</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.632041417096389e-09</v>
+        <v>4.433811432457172e-16</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.467469035176805e-09</v>
+        <v>6.038483587294922e-16</v>
       </c>
       <c r="EF7" t="n">
-        <v>8.763367809194733e-10</v>
+        <v>1.313017535274413e-16</v>
       </c>
       <c r="EG7" t="n">
-        <v>3.536942294601886e-09</v>
+        <v>9.216666084236528e-16</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.128492965740691e-09</v>
+        <v>6.029660680358085e-16</v>
       </c>
       <c r="EI7" t="n">
-        <v>4.375293016778414e-09</v>
+        <v>1.981629133178463e-15</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.180389119781466e-11</v>
+        <v>6.103943352249919e-16</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.753256067578036e-09</v>
+        <v>5.889300968250943e-16</v>
       </c>
       <c r="EL7" t="n">
-        <v>4.241115236780502e-10</v>
+        <v>4.241430662498815e-16</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.115987857680523e-10</v>
+        <v>8.608276199541655e-16</v>
       </c>
       <c r="EN7" t="n">
-        <v>7.79830977570839e-10</v>
+        <v>1.317881939611376e-15</v>
       </c>
       <c r="EO7" t="n">
-        <v>6.893754456172019e-10</v>
+        <v>8.859907982951634e-16</v>
       </c>
       <c r="EP7" t="n">
-        <v>2.133080156951905e-09</v>
+        <v>2.13336979172315e-15</v>
       </c>
       <c r="EQ7" t="n">
-        <v>5.892945853513964e-11</v>
+        <v>2.188133648136693e-15</v>
       </c>
       <c r="ER7" t="n">
-        <v>3.680387550275555e-09</v>
+        <v>3.503403973413447e-16</v>
       </c>
       <c r="ES7" t="n">
-        <v>9.027140146500301e-10</v>
+        <v>2.096901132286251e-16</v>
       </c>
       <c r="ET7" t="n">
-        <v>5.166191918704044e-10</v>
+        <v>1.754180881566422e-15</v>
       </c>
       <c r="EU7" t="n">
-        <v>5.639507749677364e-10</v>
+        <v>1.487401396202458e-15</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.674200333923181e-09</v>
+        <v>8.409445273689956e-16</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.287518618970807e-09</v>
+        <v>8.567549267250892e-16</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.334717141838638e-10</v>
+        <v>1.403999673479602e-15</v>
       </c>
       <c r="EY7" t="n">
-        <v>8.949037622052458e-10</v>
+        <v>4.443772010521291e-16</v>
       </c>
       <c r="EZ7" t="n">
-        <v>4.768339056937521e-10</v>
+        <v>6.017438524324797e-16</v>
       </c>
       <c r="FA7" t="n">
-        <v>4.915818863082677e-10</v>
+        <v>9.758843403444534e-16</v>
       </c>
       <c r="FB7" t="n">
-        <v>4.07995193185684e-10</v>
+        <v>1.300956315501104e-16</v>
       </c>
       <c r="FC7" t="n">
-        <v>2.501366891394241e-09</v>
+        <v>9.664496638614613e-16</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.197046322649499e-09</v>
+        <v>6.427972629848499e-16</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.946317995660252e-09</v>
+        <v>4.086897442206149e-16</v>
       </c>
       <c r="FF7" t="n">
-        <v>2.474416505027222e-10</v>
+        <v>1.171493999897744e-15</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.253149917168628e-09</v>
+        <v>3.015678273098803e-15</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.535269578134546e-09</v>
+        <v>9.049061557380952e-16</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.100951912442639e-10</v>
+        <v>1.192518416439779e-15</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.725791287654488e-09</v>
+        <v>7.964864678851368e-16</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.452106879185067e-09</v>
+        <v>3.973351616835526e-16</v>
       </c>
       <c r="FL7" t="n">
-        <v>7.798517387413995e-11</v>
+        <v>2.11924911721771e-15</v>
       </c>
       <c r="FM7" t="n">
-        <v>8.271725526753926e-10</v>
+        <v>1.832274989962664e-15</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.49613965660933e-09</v>
+        <v>3.397709878766075e-16</v>
       </c>
       <c r="FO7" t="n">
-        <v>2.1837418540116e-09</v>
+        <v>1.279928616706397e-15</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.000925425349465e-09</v>
+        <v>2.67725938803403e-16</v>
       </c>
       <c r="FQ7" t="n">
-        <v>6.43069686390163e-09</v>
+        <v>1.834760608146382e-15</v>
       </c>
       <c r="FR7" t="n">
-        <v>2.186795189373925e-09</v>
+        <v>1.016403961321376e-15</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.882551670107091e-09</v>
+        <v>1.456175738360165e-15</v>
       </c>
       <c r="FT7" t="n">
-        <v>1.741597088766866e-09</v>
+        <v>1.131000742821305e-15</v>
       </c>
       <c r="FU7" t="n">
-        <v>4.478282633613162e-09</v>
+        <v>5.269666191785676e-16</v>
       </c>
       <c r="FV7" t="n">
-        <v>1.349078404544457e-09</v>
+        <v>2.177768082444668e-15</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.220993528505687e-09</v>
+        <v>1.326279318371337e-15</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.205036153668516e-09</v>
+        <v>1.436543420466941e-15</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.206558186694906e-10</v>
+        <v>8.545891693580783e-16</v>
       </c>
       <c r="FZ7" t="n">
-        <v>3.104182910718123e-09</v>
+        <v>9.123156823233206e-16</v>
       </c>
       <c r="GA7" t="n">
-        <v>4.314988810705245e-09</v>
+        <v>5.60376139717119e-16</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.128333315669749e-09</v>
+        <v>8.543495119735646e-16</v>
       </c>
       <c r="GC7" t="n">
-        <v>7.75134800790056e-09</v>
+        <v>6.846739366223921e-16</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.155565225261171e-09</v>
+        <v>2.114635964028727e-15</v>
       </c>
       <c r="GE7" t="n">
-        <v>3.008560067740973e-09</v>
+        <v>1.898880049341467e-16</v>
       </c>
       <c r="GF7" t="n">
-        <v>3.11426195942488e-09</v>
+        <v>8.539934404983626e-16</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.176259756263676e-09</v>
+        <v>6.78624215554865e-16</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0005002339603379369</v>
+        <v>0.003108358243480325</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0219037439674139</v>
+        <v>0.004083606414496899</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001989144831895828</v>
+        <v>0.001271834829822183</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01235940773040056</v>
+        <v>0.01361164264380932</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005044233053922653</v>
+        <v>0.0035710115917027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003571766894310713</v>
+        <v>0.007807811256498098</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002051536925137043</v>
+        <v>0.0110104214400053</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003291623201221228</v>
+        <v>0.009453766047954559</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001431031851097941</v>
+        <v>0.003644550684839487</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001950961886905134</v>
+        <v>0.0018589380197227</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01588820107281208</v>
+        <v>0.0001257611438632011</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001114285783842206</v>
+        <v>0.0005754155572503805</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01173720881342888</v>
+        <v>0.02099724486470222</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008814927190542221</v>
+        <v>0.007997091859579086</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00533992238342762</v>
+        <v>0.009324374608695507</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0004761092131957412</v>
+        <v>0.01349337678402662</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001322230382356793</v>
+        <v>0.006184564903378487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003152168123051524</v>
+        <v>0.00250889640301466</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0007705471361987293</v>
+        <v>0.002312217839062214</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003425403265282512</v>
+        <v>0.0006682342500425875</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0007018964388407767</v>
+        <v>0.002810177858918905</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002404873725026846</v>
+        <v>0.0003881995799019933</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00154313794337213</v>
+        <v>0.003225804306566715</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001597628812305629</v>
+        <v>0.003080857684835792</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002446787431836128</v>
+        <v>0.000335203018039465</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0008641573949716985</v>
+        <v>0.002235918771475554</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001500828424468637</v>
+        <v>0.001201114850118756</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001549628446809947</v>
+        <v>0.001720725442282856</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.005212574731558561</v>
+        <v>0.002612097188830376</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001770112867234275</v>
+        <v>0.002425336977466941</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0007350189262069762</v>
+        <v>0.001705709844827652</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002809070749208331</v>
+        <v>0.002246425254270434</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001451503136195242</v>
+        <v>0.004233334679156542</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.696535274386406e-05</v>
+        <v>0.001391533995047212</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0002492775674909353</v>
+        <v>0.00315845781005919</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0002472154446877539</v>
+        <v>0.001778412028215826</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001036091824062169</v>
+        <v>0.002447767416015267</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001782441046088934</v>
+        <v>0.004048711620271206</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0005705986986868083</v>
+        <v>0.003960145637392998</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0006579800974577665</v>
+        <v>0.002716704271733761</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003925449680536985</v>
+        <v>0.0006079987506382167</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003327477723360062</v>
+        <v>0.002881405875086784</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.458524148911238e-05</v>
+        <v>0.003624804317951202</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0001874908630270511</v>
+        <v>0.001105875009670854</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0009941704338416457</v>
+        <v>0.0001092272941605188</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.00197240523993969</v>
+        <v>0.004947410430759192</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0154118537902832</v>
+        <v>0.001730380114167929</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0002134680398739874</v>
+        <v>0.004446716047823429</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003029341343790293</v>
+        <v>0.004148377571254969</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0005636792629957199</v>
+        <v>0.01335551496595144</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001615029177628458</v>
+        <v>0.008304217830300331</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.002428005682304502</v>
+        <v>0.001875235233455896</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002287623938173056</v>
+        <v>0.00142482784576714</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.753875979688019e-05</v>
+        <v>0.001336134737357497</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0006055596750229597</v>
+        <v>0.001308563631027937</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.004281566943973303</v>
+        <v>0.001512387068942189</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003797059878706932</v>
+        <v>0.0007048777770251036</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002598125254735351</v>
+        <v>0.0002536189276725054</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.006053591147065163</v>
+        <v>0.006930219940841198</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004056451376527548</v>
+        <v>0.0006548554520122707</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002799168461933732</v>
+        <v>0.002066720277070999</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0006275298655964434</v>
+        <v>0.004900844767689705</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001723391120322049</v>
+        <v>0.0007316486444324255</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.00185580353718251</v>
+        <v>0.0002116061514243484</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0050608916208148</v>
+        <v>0.003104937262833118</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002470457227900624</v>
+        <v>0.0007560516241937876</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0009922601748257875</v>
+        <v>0.00416064728051424</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.004319705534726381</v>
+        <v>0.0005623632459901273</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001839787466451526</v>
+        <v>0.0004949833964928985</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0004926368128508329</v>
+        <v>0.001461271429434419</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0003591757849790156</v>
+        <v>0.0006151497364044189</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001734448364004493</v>
+        <v>0.001254784758202732</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001414074329659343</v>
+        <v>0.001560199307277799</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.008095705881714821</v>
+        <v>0.002183818025514483</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.00274586514569819</v>
+        <v>0.003038241062313318</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002626449801027775</v>
+        <v>0.006937881466001272</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0006492373067885637</v>
+        <v>0.004147324245423079</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002342982916161418</v>
+        <v>0.004761597607284784</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0002484030555933714</v>
+        <v>0.001345111289992929</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001676759915426373</v>
+        <v>0.000900110462680459</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001903385506011546</v>
+        <v>0.001074656611308455</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0003932554973289371</v>
+        <v>0.0005778229678981006</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.003802979597821832</v>
+        <v>0.0006011045770719647</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001161593245342374</v>
+        <v>0.0003230682923458517</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001224795007146895</v>
+        <v>0.005210602656006813</v>
       </c>
       <c r="CH9" t="n">
-        <v>9.472640522290021e-05</v>
+        <v>0.0006670050206594169</v>
       </c>
       <c r="CI9" t="n">
-        <v>9.480871813138947e-05</v>
+        <v>0.001185317058116198</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0003598161856643856</v>
+        <v>0.0008468290907330811</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0001866052916739136</v>
+        <v>0.001741054002195597</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.201896131737158e-05</v>
+        <v>0.0005553684895858169</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.00394021300598979</v>
+        <v>0.001070927595719695</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002472511725500226</v>
+        <v>0.0001774172415025532</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.000815748586319387</v>
+        <v>0.004894375801086426</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.003613188397139311</v>
+        <v>0.007308443076908588</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.002168965293094516</v>
+        <v>0.0004773128312081099</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002045147586613894</v>
+        <v>0.001314483117312193</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.002827707910910249</v>
+        <v>0.003672321792691946</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.004886836279183626</v>
+        <v>0.002377668395638466</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001415252772858366</v>
+        <v>0.00253533199429512</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0004740357107948512</v>
+        <v>0.0001409672549925745</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.003048804355785251</v>
+        <v>0.0001831988338381052</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.001789150643162429</v>
+        <v>1.283723395317793e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001834817114286125</v>
+        <v>0.005728315562009811</v>
       </c>
       <c r="CZ9" t="n">
-        <v>6.63468090351671e-05</v>
+        <v>0.002327001886442304</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.000330854207277298</v>
+        <v>0.001405752147547901</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005507961031980813</v>
+        <v>0.001186936162412167</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.000295630656182766</v>
+        <v>0.001724822912365198</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001213618088513613</v>
+        <v>0.001241289079189301</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001597779570147395</v>
+        <v>0.002574393525719643</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.004455768968909979</v>
+        <v>0.001006589736789465</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001238275552168489</v>
+        <v>5.187792703509331e-05</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.005254770163446665</v>
+        <v>0.002814139239490032</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002006718888878822</v>
+        <v>0.003711775643751025</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0009124425705522299</v>
+        <v>0.0075654536485672</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001860539545305073</v>
+        <v>0.001230163383297622</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001394577906467021</v>
+        <v>0.007395879365503788</v>
       </c>
       <c r="DM9" t="n">
-        <v>7.736816769465804e-06</v>
+        <v>0.003967490047216415</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001121578272432089</v>
+        <v>0.002315288409590721</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001530700945295393</v>
+        <v>0.002517173998057842</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001985404873266816</v>
+        <v>0.001001396216452122</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0002337705809623003</v>
+        <v>0.0003120173932984471</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001584492740221322</v>
+        <v>0.001785101019777358</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0003934501146432012</v>
+        <v>0.0008542940486222506</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001472869655117393</v>
+        <v>0.0004239323316141963</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0002271361881867051</v>
+        <v>0.004543137736618519</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.000928469467908144</v>
+        <v>0.006804277189075947</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0002617125574033707</v>
+        <v>0.001942662172950804</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001493326271884143</v>
+        <v>0.002204781165346503</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.001187732559628785</v>
+        <v>0.00391827616840601</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001446234236937016</v>
+        <v>0.003713932121172547</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001960143679752946</v>
+        <v>0.00047032639849931</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.00223329127766192</v>
+        <v>0.004387519787997007</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0005487565067596734</v>
+        <v>0.002498546615242958</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001036500791087747</v>
+        <v>0.005677721928805113</v>
       </c>
       <c r="EE9" t="n">
-        <v>4.028320836368948e-05</v>
+        <v>0.003258001524955034</v>
       </c>
       <c r="EF9" t="n">
-        <v>2.29793949984014e-05</v>
+        <v>0.003145766677334905</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001867395360022783</v>
+        <v>0.0008616511477157474</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001006280654110014</v>
+        <v>0.00267995847389102</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001778459292836487</v>
+        <v>0.005986801348626614</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.002422461751848459</v>
+        <v>0.0001490708527853712</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001496254844823852</v>
+        <v>0.000491066777613014</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0009206124232150614</v>
+        <v>2.806761767715216e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004936471814289689</v>
+        <v>0.001059974078088999</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0005280456971377134</v>
+        <v>0.0002968558692373335</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001211153576150537</v>
+        <v>0.000396245566662401</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.003086702432483435</v>
+        <v>0.002886786824092269</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001129275071434677</v>
+        <v>6.600475171580911e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.001374098006635904</v>
+        <v>0.005227014422416687</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0005065661971457303</v>
+        <v>0.001946598757058382</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.002312059514224529</v>
+        <v>0.0008697306620888412</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002129854867234826</v>
+        <v>0.002478752285242081</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0008687431691214442</v>
+        <v>0.001762738218531013</v>
       </c>
       <c r="EW9" t="n">
-        <v>9.764450805960223e-05</v>
+        <v>0.006476128473877907</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0002085811865981668</v>
+        <v>0.0005463155684992671</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003110541729256511</v>
+        <v>0.000907130423001945</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0009449692443013191</v>
+        <v>0.0005625304765999317</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001646725926548243</v>
+        <v>0.005890674889087677</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0004725694889202714</v>
+        <v>0.00116349384188652</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0008606297778896987</v>
+        <v>0.001604443299584091</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0007013215217739344</v>
+        <v>0.001476001343689859</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0002809004508890212</v>
+        <v>0.002098794560879469</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.000506799085997045</v>
+        <v>0.0001925920369103551</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0003381982096470892</v>
+        <v>0.001309124054387212</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0004062045481987298</v>
+        <v>0.0007994613843038678</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0006474434630945325</v>
+        <v>0.001293163746595383</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.001529341447167099</v>
+        <v>0.0008167509222403169</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0003520643804222345</v>
+        <v>0.00083045510109514</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.001263656304217875</v>
+        <v>0.0004401714541018009</v>
       </c>
       <c r="FM9" t="n">
-        <v>6.934429984539747e-05</v>
+        <v>0.002079276833683252</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0003247644635848701</v>
+        <v>0.002786421915516257</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001502092054579407</v>
+        <v>0.001528566586785018</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.002302437555044889</v>
+        <v>0.004021084867417812</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001027770049404353</v>
+        <v>0.003281982382759452</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0005970579222775996</v>
+        <v>0.006938369013369083</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.001626461511477828</v>
+        <v>0.004038605373352766</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0005026684375479817</v>
+        <v>0.005301078781485558</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.001552068395540118</v>
+        <v>0.003601980395615101</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001433545490726829</v>
+        <v>0.003865296253934503</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0009589679539203644</v>
+        <v>0.01190153229981661</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.000718605297151953</v>
+        <v>0.0005950834602117538</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.00278632203117013</v>
+        <v>0.0004648794129025191</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.001240072306245565</v>
+        <v>0.003411062993109226</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0005186635535210371</v>
+        <v>0.002179400995373726</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0008106117602437735</v>
+        <v>0.004929692950099707</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0006394615629687905</v>
+        <v>0.0005145741160959005</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.003494036616757512</v>
+        <v>0.005589131731539965</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.004501057788729668</v>
+        <v>0.003441947977989912</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0004950626171194017</v>
+        <v>0.001962576759979129</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0006159006152302027</v>
+        <v>0.0006655334727838635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.03813327848911285</v>
+        <v>0.01477304566651583</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2362513095140457</v>
+        <v>0.01150975748896599</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02455025911331177</v>
+        <v>0.005437811370939016</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06357952207326889</v>
+        <v>0.1013995036482811</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006989554967731237</v>
+        <v>0.03303579613566399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03312736004590988</v>
+        <v>0.005591860506683588</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01923612877726555</v>
+        <v>0.06681827455759048</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006990948691964149</v>
+        <v>0.0510963462293148</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004012618213891983</v>
+        <v>0.04305886477231979</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04114924743771553</v>
+        <v>0.009488393552601337</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1487133055925369</v>
+        <v>0.01001940481364727</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002581879496574402</v>
+        <v>0.009960180148482323</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09351742267608643</v>
+        <v>0.1332397758960724</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04193767532706261</v>
+        <v>0.06379934400320053</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06364700198173523</v>
+        <v>0.004478008486330509</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01600231789052486</v>
+        <v>0.07430791109800339</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01181929931044579</v>
+        <v>0.03158184885978699</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005137236788868904</v>
+        <v>0.04120715707540512</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009602325037121773</v>
+        <v>0.006919466890394688</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04027817025780678</v>
+        <v>0.001199260819703341</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02075465954840183</v>
+        <v>0.004745423793792725</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02090383879840374</v>
+        <v>0.01170931477099657</v>
       </c>
       <c r="W10" t="n">
-        <v>0.007020012941211462</v>
+        <v>0.01726451888680458</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02503825724124908</v>
+        <v>0.003394176950678229</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003030918538570404</v>
+        <v>0.001544179976917803</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.004771965555846691</v>
+        <v>0.008648641407489777</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.002820727648213506</v>
+        <v>0.005600085016340017</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.02962575852870941</v>
+        <v>0.0006253229803405702</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03669612854719162</v>
+        <v>0.008965492248535156</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01851680502295494</v>
+        <v>0.009249520488083363</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.006594614125788212</v>
+        <v>0.009351270273327827</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02325155586004257</v>
+        <v>0.009663376025855541</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002905999077484012</v>
+        <v>0.0129215819761157</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01978744193911552</v>
+        <v>0.01788236573338509</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01615745574235916</v>
+        <v>0.01161598041653633</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.009246628731489182</v>
+        <v>0.006081650033593178</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02974751219153404</v>
+        <v>0.01122852135449648</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.009785977192223072</v>
+        <v>0.01543071586638689</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01949822530150414</v>
+        <v>0.005617424380034208</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02344945259392262</v>
+        <v>0.01684251986443996</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02800550125539303</v>
+        <v>0.009889830835163593</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02195976860821247</v>
+        <v>0.006113769486546516</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00671682134270668</v>
+        <v>0.03341981768608093</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0161048099398613</v>
+        <v>0.005345758050680161</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.006397988181561232</v>
+        <v>0.007239319384098053</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.00767748337239027</v>
+        <v>0.03728599473834038</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1911274939775467</v>
+        <v>0.008123529143631458</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0154460621997714</v>
+        <v>0.01317956112325191</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.007263717241585255</v>
+        <v>0.0189579613506794</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04599688202142715</v>
+        <v>0.05918347835540771</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02370000071823597</v>
+        <v>0.0002891371259465814</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001734257210046053</v>
+        <v>0.001236489973962307</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01211097463965416</v>
+        <v>0.001873803790658712</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.009556401520967484</v>
+        <v>0.01504801772534847</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.006427675485610962</v>
+        <v>0.0009892936795949936</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.05275484919548035</v>
+        <v>6.492179818451405e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03478188812732697</v>
+        <v>0.0111698042601347</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.01153830904513597</v>
+        <v>0.01547660119831562</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0478493757545948</v>
+        <v>0.01554261799901724</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.05076494067907333</v>
+        <v>0.001875960384495556</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.004534322768449783</v>
+        <v>0.02050316706299782</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01478424668312073</v>
+        <v>0.02864914573729038</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.002470606006681919</v>
+        <v>0.006061800755560398</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.06056644767522812</v>
+        <v>0.006810464430600405</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.06615100800991058</v>
+        <v>0.01532680541276932</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.01718035712838173</v>
+        <v>0.01114983670413494</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02467199414968491</v>
+        <v>0.03346164524555206</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.04356911033391953</v>
+        <v>0.002500070026144385</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.007579325698316097</v>
+        <v>0.001393147744238377</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0005037486553192139</v>
+        <v>0.0047972546890378</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0201849602162838</v>
+        <v>0.003563388250768185</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.01321034226566553</v>
+        <v>0.000516922096721828</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01320471428334713</v>
+        <v>0.01262897625565529</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.09169335663318634</v>
+        <v>0.0132210785523057</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001694716396741569</v>
+        <v>0.005998998880386353</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01462467014789581</v>
+        <v>0.0586046576499939</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01820147596299648</v>
+        <v>0.02423065155744553</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.05647195875644684</v>
+        <v>0.0008681451436132193</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.01327446103096008</v>
+        <v>0.005506737157702446</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.002705238061025739</v>
+        <v>0.003887653117999434</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0003628474660217762</v>
+        <v>0.01046376954764128</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01891803741455078</v>
+        <v>0.004710654728114605</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.04209610819816589</v>
+        <v>0.003780149621888995</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001246668281964958</v>
+        <v>0.003652639221400023</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002506268676370382</v>
+        <v>0.03433310613036156</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0147927962243557</v>
+        <v>0.00853313971310854</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001108522643335164</v>
+        <v>0.001381437294185162</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.006276114378124475</v>
+        <v>0.007065322250127792</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.002151428489014506</v>
+        <v>0.009929112158715725</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001753650140017271</v>
+        <v>0.004551386460661888</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.04278496280312538</v>
+        <v>0.01854358986020088</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0523604042828083</v>
+        <v>0.007620728574693203</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02467120811343193</v>
+        <v>0.005776186008006334</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.06068278104066849</v>
+        <v>0.03918924182653427</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.03186450153589249</v>
+        <v>0.01734642125666142</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.04823129996657372</v>
+        <v>0.002084507839754224</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.01505567319691181</v>
+        <v>0.04437894001603127</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01287337951362133</v>
+        <v>0.001945347292348742</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.007513168733566999</v>
+        <v>0.01879234798252583</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0194510817527771</v>
+        <v>0.003478835802525282</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.03272660449147224</v>
+        <v>0.005263824481517076</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.004989349748939276</v>
+        <v>0.002210668521001935</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.009308384731411934</v>
+        <v>0.03861640021204948</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0179445669054985</v>
+        <v>0.01179328374564648</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.004814701154828072</v>
+        <v>0.001520666759461164</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.003902458120137453</v>
+        <v>0.002713905647397041</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.002141491277143359</v>
+        <v>0.009276075288653374</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.00149028142914176</v>
+        <v>0.008054615929722786</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.00553519930690527</v>
+        <v>0.02818556129932404</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.03023683279752731</v>
+        <v>0.007120301481336355</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.01189342699944973</v>
+        <v>0.02174538932740688</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.008012231439352036</v>
+        <v>0.0488019697368145</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.009846663102507591</v>
+        <v>0.01480695512145758</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.01636092737317085</v>
+        <v>0.02324348501861095</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01352506596595049</v>
+        <v>0.008115959353744984</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.004157655872404575</v>
+        <v>0.04248181730508804</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001675110543146729</v>
+        <v>0.0004836949519813061</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.03904029354453087</v>
+        <v>0.00839122012257576</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.02000529691576958</v>
+        <v>0.004212894011288881</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.02240589633584023</v>
+        <v>0.009527280926704407</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.004012496210634708</v>
+        <v>0.01240921299904585</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01418687682598829</v>
+        <v>0.004945688415318727</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01977304741740227</v>
+        <v>0.01327813230454922</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.005345210433006287</v>
+        <v>0.00877884216606617</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.01096598710864782</v>
+        <v>0.01792142726480961</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.008898241445422173</v>
+        <v>0.04236160591244698</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.008751191198825836</v>
+        <v>0.008831476792693138</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.007973814383149147</v>
+        <v>0.007742251269519329</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.02721463516354561</v>
+        <v>0.02122828364372253</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01468936819583178</v>
+        <v>0.005254478193819523</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.03592098504304886</v>
+        <v>0.01214544661343098</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.005810013506561518</v>
+        <v>0.00234094331972301</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.001327071571722627</v>
+        <v>0.005600918084383011</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.008547942154109478</v>
+        <v>0.02172180823981762</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.004483101423829794</v>
+        <v>0.007963054813444614</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02295380830764771</v>
+        <v>0.01519640907645226</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.03883733227849007</v>
+        <v>0.005763237364590168</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02011519484221935</v>
+        <v>0.005050778388977051</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.006403663195669651</v>
+        <v>0.03766646236181259</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.006380858365446329</v>
+        <v>0.01109124999493361</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.007510665338486433</v>
+        <v>0.002080149482935667</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0003557367017492652</v>
+        <v>0.006006251089274883</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.008468115702271461</v>
+        <v>0.006914281286299229</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.000114180613309145</v>
+        <v>0.005167073104530573</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01848163828253746</v>
+        <v>0.01167588122189045</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.02002829872071743</v>
+        <v>0.007576475851237774</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.02063846774399281</v>
+        <v>0.00174627872183919</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01749447360634804</v>
+        <v>0.04387646913528442</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01682075299322605</v>
+        <v>0.006517233792692423</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03937764093279839</v>
+        <v>0.01325988583266735</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01022093649953604</v>
+        <v>0.006842285860329866</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00983123853802681</v>
+        <v>0.01683742552995682</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.01154042221605778</v>
+        <v>0.02542879618704319</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01459584664553404</v>
+        <v>0.005782315041869879</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.03544452413916588</v>
+        <v>0.002081056823953986</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001268860185518861</v>
+        <v>0.0007093871827237308</v>
       </c>
       <c r="FA10" t="n">
-        <v>3.579899203032255e-05</v>
+        <v>0.04023436456918716</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.002609977731481194</v>
+        <v>0.01175013370811939</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.008080601692199707</v>
+        <v>0.002261621877551079</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.005128444172441959</v>
+        <v>0.00255208951421082</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003285769838839769</v>
+        <v>0.01091167144477367</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.001280452124774456</v>
+        <v>0.005109942518174648</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01232823636382818</v>
+        <v>0.01242821663618088</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.004381956532597542</v>
+        <v>0.009909354150295258</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.009654784575104713</v>
+        <v>0.001152495970018208</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01151607371866703</v>
+        <v>0.01142733357846737</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01963082700967789</v>
+        <v>0.007085185032337904</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.004147445783019066</v>
+        <v>0.00503888726234436</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.01183198112994432</v>
+        <v>0.01861917972564697</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001210745889693499</v>
+        <v>0.006763667799532413</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.00907488539814949</v>
+        <v>0.02206418476998806</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01154444925487041</v>
+        <v>0.01870512217283249</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.04108529537916183</v>
+        <v>0.01033014617860317</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.007302571088075638</v>
+        <v>0.004108414985239506</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.05148837342858315</v>
+        <v>0.01034226547926664</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0331539623439312</v>
+        <v>0.02184969000518322</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.02038440853357315</v>
+        <v>0.008079193532466888</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.01517719868570566</v>
+        <v>0.02705799788236618</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01409600581973791</v>
+        <v>0.03487828746438026</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.004119375720620155</v>
+        <v>0.01271546073257923</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0259535051882267</v>
+        <v>0.001105595380067825</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02574628591537476</v>
+        <v>0.00818256102502346</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01017378177493811</v>
+        <v>0.01321578305214643</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.009797429665923119</v>
+        <v>0.02773362770676613</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.02486321516335011</v>
+        <v>0.006492855027318001</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02327815629541874</v>
+        <v>0.01746264472603798</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.01891808584332466</v>
+        <v>0.005332089960575104</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01299329660832882</v>
+        <v>0.009764880873262882</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001652943901717663</v>
+        <v>0.02048849873244762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.00163335376419127</v>
+        <v>0.001195520162582397</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01570671424269676</v>
+        <v>0.00638386607170105</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001834211405366659</v>
+        <v>0.0001013005385175347</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00392219377681613</v>
+        <v>0.003000190015882254</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009942921809852123</v>
+        <v>0.002103102393448353</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001318239839747548</v>
+        <v>0.008358231745660305</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0009105345234274864</v>
+        <v>0.001922063762322068</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003374306252226233</v>
+        <v>0.00449456088244915</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001134003978222609</v>
+        <v>0.0003447195922490209</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001769008580595255</v>
+        <v>0.001136830425821245</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01193172484636307</v>
+        <v>0.007494036573916674</v>
       </c>
       <c r="L11" t="n">
-        <v>9.848922491073608e-05</v>
+        <v>0.000970424385741353</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001370026730000973</v>
+        <v>0.000628393143415451</v>
       </c>
       <c r="N11" t="n">
-        <v>0.006319242063909769</v>
+        <v>0.005993669852614403</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001023664139211178</v>
+        <v>0.009503914974629879</v>
       </c>
       <c r="P11" t="n">
-        <v>6.21904619038105e-05</v>
+        <v>0.0009292768081650138</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0006734627531841397</v>
+        <v>0.001690063276328146</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002449360443279147</v>
+        <v>0.001507071545347571</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004592932527884841</v>
+        <v>0.001282366225495934</v>
       </c>
       <c r="T11" t="n">
-        <v>0.001658244407735765</v>
+        <v>0.001338878879323602</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0009217114420607686</v>
+        <v>0.001740454928949475</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001941492548212409</v>
+        <v>0.0007265154272317886</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006015778053551912</v>
+        <v>8.47950141178444e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>7.502106018364429e-05</v>
+        <v>0.0009500123560428619</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0007170719327405095</v>
+        <v>0.0005164726171642542</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003079110756516457</v>
+        <v>0.001863876939751208</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0006569350953213871</v>
+        <v>0.0001065130345523357</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0005251952679827809</v>
+        <v>0.001640283386223018</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.002217151923105121</v>
+        <v>0.0008696355507709086</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0003487751237116754</v>
+        <v>0.0006911934469826519</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0005249999230727553</v>
+        <v>0.001162785338237882</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001141934189945459</v>
+        <v>0.003835347015410662</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0001088399440050125</v>
+        <v>0.002647720975801349</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0008083125576376915</v>
+        <v>0.002379461191594601</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0004623295972123742</v>
+        <v>0.004386024083942175</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0006000195862725377</v>
+        <v>0.001034129410982132</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.002100046724081039</v>
+        <v>0.0008734274888411164</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.00227694446220994</v>
+        <v>0.002214811975136399</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.00130147545132786</v>
+        <v>0.001664407784119248</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0003878551651723683</v>
+        <v>0.0008705459185875952</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.002195595065131783</v>
+        <v>7.598716911161318e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002877167658880353</v>
+        <v>0.0006310096941888332</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0008107824251055717</v>
+        <v>0.0002740027848631144</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0001473652664572001</v>
+        <v>0.001035326858982444</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0005156854167580605</v>
+        <v>0.0005211095558479428</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0008502569398842752</v>
+        <v>0.0006028749630786479</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01187822502106428</v>
+        <v>0.008158064447343349</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0003670243313536048</v>
+        <v>0.001984248869121075</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001159887760877609</v>
+        <v>0.0003747465671040118</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.004011313430964947</v>
+        <v>0.004000592511147261</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003695472842082381</v>
+        <v>0.00523493904620409</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.004777296911925077</v>
+        <v>0.0007179309031926095</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0006668384885415435</v>
+        <v>0.001400747220031917</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.001236953190527856</v>
+        <v>0.0006429716013371944</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.002355798147618771</v>
+        <v>0.001176181249320507</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.005833140574395657</v>
+        <v>0.000785608368460089</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001559998956508934</v>
+        <v>0.0006522355834022164</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0005472492193803191</v>
+        <v>0.002349226269870996</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.003350918181240559</v>
+        <v>0.0001774639240466058</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001327960519120097</v>
+        <v>0.0001283028977923095</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002694814233109355</v>
+        <v>0.0008566163014620543</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001104084542021155</v>
+        <v>0.003247274551540613</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0001953330938704312</v>
+        <v>0.001441903063096106</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003256636206060648</v>
+        <v>0.0005076698726043105</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.005937628913670778</v>
+        <v>0.002426481572911143</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0007658386020921171</v>
+        <v>0.0005045770667493343</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.002069245325401425</v>
+        <v>0.0009313137270510197</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.00290430267341435</v>
+        <v>0.002136864466592669</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002434744499623775</v>
+        <v>0.002954678609967232</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0007186512229964137</v>
+        <v>0.001345455413684249</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.001749631832353771</v>
+        <v>0.0001159309176728129</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.001006419421173632</v>
+        <v>0.002306414535269141</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0007975557236932218</v>
+        <v>0.0005711123812943697</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.00745268864557147</v>
+        <v>0.005421783309429884</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002807326847687364</v>
+        <v>0.000846229842863977</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0001080150250345469</v>
+        <v>0.002435519825667143</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.00122743146494031</v>
+        <v>0.0001051034196279943</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001915346714667976</v>
+        <v>0.00233634514734149</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0005028403829783201</v>
+        <v>0.0006819519330747426</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.001229510409757495</v>
+        <v>0.0009103776537813246</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0003317883238196373</v>
+        <v>0.0003718193038366735</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0003772029303945601</v>
+        <v>0.001723016379401088</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.002060202183201909</v>
+        <v>0.002178481314331293</v>
       </c>
       <c r="CF11" t="n">
-        <v>7.59546019253321e-05</v>
+        <v>0.0005287773092277348</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0006579969194717705</v>
+        <v>0.0004843084025196731</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001302730874158442</v>
+        <v>2.270509139634669e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>8.686137152835727e-05</v>
+        <v>0.002255517989397049</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001197810866869986</v>
+        <v>0.0005392144084908068</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001383489929139614</v>
+        <v>0.0004250497149769217</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.000457565940450877</v>
+        <v>0.000430424086516723</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.003493615658953786</v>
+        <v>0.0007342107128351927</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.004212956875562668</v>
+        <v>0.003894743276759982</v>
       </c>
       <c r="CO11" t="n">
-        <v>4.677163087762892e-05</v>
+        <v>0.002324028639122844</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.003000545781105757</v>
+        <v>0.002342899097129703</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.003371687605977058</v>
+        <v>4.392268601804972e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0004189377650618553</v>
+        <v>0.0003131187404505908</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.002271832665428519</v>
+        <v>0.001571086584590375</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001367256161756814</v>
+        <v>0.0008030729368329048</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0007381587056443095</v>
+        <v>0.0003785243898164481</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001989667507587001</v>
+        <v>0.001303534721955657</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.00140958244446665</v>
+        <v>0.001693416503258049</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0005216308636590838</v>
+        <v>0.0001762157189659774</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001271607587113976</v>
+        <v>5.949911428615451e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0005837666103616357</v>
+        <v>0.000562182511202991</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0001809861860238016</v>
+        <v>0.002387881744652987</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0006957864970900118</v>
+        <v>5.069239705335349e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001421334454789758</v>
+        <v>0.0001741328451316804</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0005605275509878993</v>
+        <v>0.000389333232305944</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001467872643843293</v>
+        <v>0.0002622246975079179</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.00104692461900413</v>
+        <v>0.002511143451556563</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001145386253483593</v>
+        <v>0.00096281518926844</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.008735284209251404</v>
+        <v>0.0004240795969963074</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004532106220722198</v>
+        <v>0.001936798798851669</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003709994256496429</v>
+        <v>0.0002795028849504888</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.003585629630833864</v>
+        <v>0.0006963979103602469</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0009909631917253137</v>
+        <v>0.003136882092803717</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.005223530344665051</v>
+        <v>0.003763510612770915</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001157003687694669</v>
+        <v>0.0006991991540417075</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.001487714005634189</v>
+        <v>0.0009128303499892354</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001519755693152547</v>
+        <v>0.0006117960438132286</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001678087166510522</v>
+        <v>0.001603425480425358</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002061758190393448</v>
+        <v>0.001467180554755032</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0009470091899856925</v>
+        <v>3.885434125550091e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.002008038340136409</v>
+        <v>0.001027736347168684</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0002294160367455333</v>
+        <v>0.002141291275620461</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.002128669060766697</v>
+        <v>0.0002609182265587151</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0009616164606995881</v>
+        <v>0.0005783973610959947</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.001277912058867514</v>
+        <v>0.0002563328598625958</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001096588908694685</v>
+        <v>0.0009980344912037253</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001082171453163028</v>
+        <v>0.0005710253026336432</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0002122609876096249</v>
+        <v>0.0007370540988631546</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001691214274615049</v>
+        <v>0.001749147195369005</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.000179883383680135</v>
+        <v>0.0004415962030179799</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007753595127724111</v>
+        <v>0.0006644865497946739</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.002707620849832892</v>
+        <v>0.00291661242954433</v>
       </c>
       <c r="EF11" t="n">
-        <v>1.050328137353063e-05</v>
+        <v>0.001125423586927354</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001814113813452423</v>
+        <v>0.0002070574555546045</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0001689485943643376</v>
+        <v>0.001373193459585309</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0002679853932932019</v>
+        <v>0.0002362029626965523</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001556126167997718</v>
+        <v>0.0008072061464190483</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.002082952298223972</v>
+        <v>0.001637444132938981</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.001081528607755899</v>
+        <v>0.0001506677072029561</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001298870076425374</v>
+        <v>0.0002291693381266668</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0003386845346540213</v>
+        <v>0.000169384918990545</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001820954494178295</v>
+        <v>0.001831759349443018</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0007356919813901186</v>
+        <v>0.001604093471542001</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001758027821779251</v>
+        <v>0.0003546507214196026</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.002263541333377361</v>
+        <v>0.0003341339761391282</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0008443845435976982</v>
+        <v>0.002724823309108615</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001607159152626991</v>
+        <v>0.0008003370021469891</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001652961364015937</v>
+        <v>0.0004594076308421791</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003351969178766012</v>
+        <v>0.001570505439303815</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001145280548371375</v>
+        <v>0.00040847432683222</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0002349771384615451</v>
+        <v>0.001783711370080709</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001112997182644904</v>
+        <v>0.002303156536072493</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0001535007613711059</v>
+        <v>0.000248283613473177</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0003744782879948616</v>
+        <v>0.0002003677072934806</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001027214340865612</v>
+        <v>0.0001940246584126726</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.00022349480423145</v>
+        <v>0.001877607661299407</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001638848450966179</v>
+        <v>0.0004337608406785876</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001716182800009847</v>
+        <v>0.0002253964921692386</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001127374125644565</v>
+        <v>0.0004786570207215846</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0004427471722010523</v>
+        <v>0.0003728162846527994</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001726811402477324</v>
+        <v>0.002152581932023168</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0002622113679535687</v>
+        <v>0.0009786565788090229</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.003011356107890606</v>
+        <v>0.002842878922820091</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001191347022540867</v>
+        <v>0.001318641239777207</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0002017614606302232</v>
+        <v>0.002658119658008218</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.002692961599677801</v>
+        <v>0.001491638598963618</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0009798724204301834</v>
+        <v>0.004556791391223669</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0005028826417401433</v>
+        <v>0.001484798034653068</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.003327382262796164</v>
+        <v>0.0004920852952636778</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0002334992605028674</v>
+        <v>0.002780648646876216</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.00105323689058423</v>
+        <v>0.00205689505673945</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0003856330877169967</v>
+        <v>0.001253462978638709</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.007772539742290974</v>
+        <v>5.524983862414956e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.001994864316657186</v>
+        <v>8.097360841929913e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.002142977900803089</v>
+        <v>0.0007796057034283876</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0001002788485493511</v>
+        <v>0.004979366436600685</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.001992925303056836</v>
+        <v>0.001085768104530871</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.002062958665192127</v>
+        <v>0.002429685089737177</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.00146471441257745</v>
+        <v>0.0005439806263893843</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.002266341354697943</v>
+        <v>0.001823457307182252</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.001648269477300346</v>
+        <v>4.497996997088194e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0006898858118802309</v>
+        <v>0.002022101311013103</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.00352860358543694</v>
+        <v>0.00244339881464839</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001560988137498498</v>
+        <v>0.0007007299573160708</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001042685937136412</v>
+        <v>0.001272989669814706</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001653502928093076</v>
+        <v>0.001655230531468987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0002838517248164862</v>
+        <v>5.076435627415776e-07</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008749171160161495</v>
+        <v>0.002056613797321916</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004295927938073874</v>
+        <v>0.0002209858503192663</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005564824678003788</v>
+        <v>0.003629906801506877</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001087204436771572</v>
+        <v>0.000477505789604038</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0009824491571635008</v>
+        <v>0.002389984671026468</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006667630514129996</v>
+        <v>0.002298380248248577</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0009513979312032461</v>
+        <v>0.002915967023000121</v>
       </c>
       <c r="I12" t="n">
-        <v>8.516386151313782e-05</v>
+        <v>0.001114652492105961</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0009010235080495477</v>
+        <v>1.546717248857021e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.005876097828149796</v>
+        <v>0.001283486839383841</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005627471255138516</v>
+        <v>0.0002248751698061824</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005368889309465885</v>
+        <v>0.005004536360502243</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002707690699025989</v>
+        <v>0.00183390686288476</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002359977224841714</v>
+        <v>0.002826636889949441</v>
       </c>
       <c r="P12" t="n">
-        <v>9.627343388274312e-05</v>
+        <v>0.002429052256047726</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0008954107761383057</v>
+        <v>0.001993359299376607</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0008724905783310533</v>
+        <v>0.0006206273101270199</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002549400378484279</v>
+        <v>0.0001247336040250957</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001569964340887964</v>
+        <v>0.000134791320306249</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0005648528458550572</v>
+        <v>0.0005000662058591843</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0007576097850687802</v>
+        <v>0.0003779252001550049</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0002998114214278758</v>
+        <v>0.0008676834404468536</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0009026550687849522</v>
+        <v>0.0009811522904783487</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0008679952588863671</v>
+        <v>5.811089067719877e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002864968846552074</v>
+        <v>0.0004660797421820462</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0004290605138521641</v>
+        <v>0.0001330887025687844</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0008069389150477946</v>
+        <v>0.0001352766412310302</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.001810579444281757</v>
+        <v>0.0003496545250527561</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0001903038646560162</v>
+        <v>0.0002174157998524606</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.753376611508429e-05</v>
+        <v>0.0004206785815767944</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0002784515672829002</v>
+        <v>0.0005550315254367888</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.000158011622261256</v>
+        <v>0.001162574393674731</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0008545274613425136</v>
+        <v>0.0005467223818413913</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0002117934636771679</v>
+        <v>0.000652895076200366</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001726702612359077</v>
+        <v>0.0004990999586880207</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0003817574470303953</v>
+        <v>0.0001908414997160435</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0006588862743228674</v>
+        <v>0.0006044680485501885</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003855835821013898</v>
+        <v>0.0008471244946122169</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.000510514946654439</v>
+        <v>0.0007589398301206529</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001035264460369945</v>
+        <v>0.0002328163682250306</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.001123534981161356</v>
+        <v>0.0007983879186213017</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0004430368135217577</v>
+        <v>0.0008571729995310307</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0006507677026093006</v>
+        <v>0.0001314288092544302</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001210067493957467</v>
+        <v>4.75598790217191e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.000914205564185977</v>
+        <v>0.0007183184497989714</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.006596624851226807</v>
+        <v>0.0008270185207948089</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0002095621020998806</v>
+        <v>0.001036137458868325</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0003115249273832887</v>
+        <v>0.001235006609931588</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.001330181956291199</v>
+        <v>0.003264385275542736</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0006149420514702797</v>
+        <v>0.001987585332244635</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.104757241904736e-05</v>
+        <v>0.0001486150431446731</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0008329770062118769</v>
+        <v>5.767185575678013e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001920951472129673</v>
+        <v>0.0006821225397288799</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0003174807643517852</v>
+        <v>6.986616062931716e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001417805440723896</v>
+        <v>0.0009170157136395574</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001561812125146389</v>
+        <v>0.000188157195225358</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.001558271702378988</v>
+        <v>0.0002384621766395867</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.00287640537135303</v>
+        <v>0.001830383436754346</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.001029375474900007</v>
+        <v>0.0001177846279460937</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.001112927799113095</v>
+        <v>0.0007804876076988876</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0007763220928609371</v>
+        <v>0.001841113204136491</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0005677877343259752</v>
+        <v>0.0001022052165353671</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.001341711264103651</v>
+        <v>0.000288814801024273</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.001931708538904786</v>
+        <v>0.0007535460754297674</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0006454463000409305</v>
+        <v>6.373492942657322e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.480592906475067e-06</v>
+        <v>0.0008601091103628278</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.001630833372473717</v>
+        <v>0.0004399765166454017</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0008187490748241544</v>
+        <v>1.121619789046235e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.001000469783321023</v>
+        <v>0.0003016876871697605</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.001202716026455164</v>
+        <v>0.0001408536336384714</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001389552489854395</v>
+        <v>0.0003908196813426912</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0007265681633725762</v>
+        <v>0.0001845572551246732</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.003529686480760574</v>
+        <v>0.0004797449219040573</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0005015149363316596</v>
+        <v>0.0006653507589362562</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0004300580767448992</v>
+        <v>0.001596474903635681</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.000612173113040626</v>
+        <v>0.0009821930434554815</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001606479054316878</v>
+        <v>0.001537092728540301</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0002993987582158297</v>
+        <v>0.0003104301576968282</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.462493234314024e-05</v>
+        <v>0.0003344203578308225</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0005052762571722269</v>
+        <v>0.0001586428115842864</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0004684265586547554</v>
+        <v>4.185510624665767e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.001519171055406332</v>
+        <v>0.000415047921705991</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0004230998747516423</v>
+        <v>9.252584277419373e-06</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0003362942370586097</v>
+        <v>0.001337422989308834</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0004773502005264163</v>
+        <v>0.0002123510639648885</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0002419863303657621</v>
+        <v>0.0004562530957628042</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0005958289839327335</v>
+        <v>1.68638325703796e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.534739905968308e-06</v>
+        <v>0.000457305897725746</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0002276856248499826</v>
+        <v>0.0002222606417490169</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.001387936063110828</v>
+        <v>0.0003265865962021053</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.00116197788156569</v>
+        <v>0.0002758869668468833</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0004144897102378309</v>
+        <v>0.001564003177918494</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.002186010126024485</v>
+        <v>0.001922355615533888</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.001356192049570382</v>
+        <v>0.0005068032769486308</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.001536421361379325</v>
+        <v>0.0006035765400156379</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0009102976764552295</v>
+        <v>0.0008614256512373686</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.001099107437767088</v>
+        <v>0.000459418457467109</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.288753992412239e-06</v>
+        <v>0.0005347036640159786</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.000469462014734745</v>
+        <v>4.410651308717206e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.00113792868796736</v>
+        <v>0.0003264661063440144</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0006508893566206098</v>
+        <v>3.438430940150283e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0007337321876548231</v>
+        <v>0.00144339888356626</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0004753515240736306</v>
+        <v>0.0004835135769098997</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0003005804901476949</v>
+        <v>0.0004548213619273156</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0006467939238063991</v>
+        <v>0.0001173628406831995</v>
       </c>
       <c r="DC12" t="n">
-        <v>9.046385821420699e-05</v>
+        <v>0.0004087786073796451</v>
       </c>
       <c r="DD12" t="n">
-        <v>7.648416794836521e-05</v>
+        <v>0.0002614620607346296</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.000351414259057492</v>
+        <v>0.0006024667527526617</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.002119462238624692</v>
+        <v>0.0004354291595518589</v>
       </c>
       <c r="DG12" t="n">
-        <v>5.526236418518238e-05</v>
+        <v>3.525847569108009e-05</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.002528024138882756</v>
+        <v>0.001041896408423781</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0004572462639771402</v>
+        <v>0.000201890739845112</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0007754390244372189</v>
+        <v>0.0008749291300773621</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.000579338928218931</v>
+        <v>0.0001212792558362707</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0001048493577400222</v>
+        <v>0.001686951494775712</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.282215816900134e-05</v>
+        <v>0.0002561290748417377</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0009299363009631634</v>
+        <v>0.0002973573282361031</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0007013913709670305</v>
+        <v>0.0006960754981264472</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0008009483572095633</v>
+        <v>5.333797889761627e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0008177476120181382</v>
+        <v>0.0003046739439014345</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.001324468874372542</v>
+        <v>0.0001173077107523568</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0006407826440408826</v>
+        <v>0.0005141387809999287</v>
       </c>
       <c r="DT12" t="n">
-        <v>6.936673889867961e-05</v>
+        <v>0.0002851733297575265</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001215270094689913</v>
+        <v>0.001060674549080431</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.000287078000837937</v>
+        <v>0.001355165033601224</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.000148779436131008</v>
+        <v>0.0001783035113476217</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0003418640699237585</v>
+        <v>0.0005869471351616085</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0007607776205986738</v>
+        <v>0.0008342551300302148</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0006045267218723893</v>
+        <v>0.0005685008363798261</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.001151094329543412</v>
+        <v>0.0002142635057680309</v>
       </c>
       <c r="EB12" t="n">
-        <v>5.391058220993727e-05</v>
+        <v>0.0004246578901074827</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0003186188696417958</v>
+        <v>0.0001557489158585668</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0002227945369668305</v>
+        <v>0.001360189635306597</v>
       </c>
       <c r="EE12" t="n">
-        <v>2.389252767898142e-05</v>
+        <v>0.0009982601040974259</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.000266574730630964</v>
+        <v>0.0004233106155879796</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0005864576669409871</v>
+        <v>0.0001750964729581028</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0002319783961866051</v>
+        <v>0.0005247740773484111</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.000295036647003144</v>
+        <v>0.001426143338903785</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0009560099570080638</v>
+        <v>0.0003010000218637288</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002118984994012862</v>
+        <v>0.0005192760145291686</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0009810286574065685</v>
+        <v>1.840668119257316e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0003494150587357581</v>
+        <v>0.0003232360468246043</v>
       </c>
       <c r="EN12" t="n">
-        <v>6.8759145506192e-05</v>
+        <v>6.660029612248763e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0005383712705224752</v>
+        <v>3.888319770339876e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.001153277233242989</v>
+        <v>0.0007170259486883879</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0002862717083189636</v>
+        <v>0.0001214483636431396</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0006622124928981066</v>
+        <v>0.001456351019442081</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0001359931047772989</v>
+        <v>0.0002135598624590784</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001651979167945683</v>
+        <v>0.0001928418059833348</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0009161233901977539</v>
+        <v>0.0005836161435581744</v>
       </c>
       <c r="EV12" t="n">
-        <v>4.473913577385247e-07</v>
+        <v>0.0004811635590158403</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001869442203314975</v>
+        <v>0.001195125398226082</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0002641055325511843</v>
+        <v>4.267846452421509e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.001225364278070629</v>
+        <v>0.0005571831716224551</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0003332934866193682</v>
+        <v>5.538604091270827e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0006826695171184838</v>
+        <v>0.001535912742838264</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0002584250760264695</v>
+        <v>0.0003150900593027472</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0005396349006332457</v>
+        <v>0.0006065816269256175</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0006734185153618455</v>
+        <v>0.0001568854786455631</v>
       </c>
       <c r="FE12" t="n">
-        <v>3.633798041846603e-05</v>
+        <v>0.0005134562961757183</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0002025230933213606</v>
+        <v>4.156562499701977e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.000195089538465254</v>
+        <v>0.0004239086410962045</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001207683817483485</v>
+        <v>0.0001170493851532228</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0002695991424843669</v>
+        <v>0.0005177765269763768</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001114442478865385</v>
+        <v>0.0002843851980287582</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.000713706889655441</v>
+        <v>9.479017171543092e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0002682686317712069</v>
+        <v>0.0001344958000117913</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0003548623935785145</v>
+        <v>0.0004662366700358689</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0002064079890260473</v>
+        <v>0.0008112199720926583</v>
       </c>
       <c r="FO12" t="n">
-        <v>6.762366683688015e-05</v>
+        <v>0.0003534399147611111</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0002794202009681612</v>
+        <v>0.0005023027770221233</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0006390961352735758</v>
+        <v>0.0001823333150241524</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0005687512457370758</v>
+        <v>0.001565210404805839</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001236076350323856</v>
+        <v>0.0008974261581897736</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001524169929325581</v>
+        <v>0.001420663553290069</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0002595721161924303</v>
+        <v>0.0001539311779197305</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.001180379185825586</v>
+        <v>0.0007335999980568886</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0008553950465284288</v>
+        <v>0.002289138734340668</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.000489325902890414</v>
+        <v>9.744241833686829e-05</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.001086053205654025</v>
+        <v>0.0002660053432919085</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0005793908494524658</v>
+        <v>0.0005521162529475987</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001216261371155269</v>
+        <v>0.001024382538162172</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0001327745558228344</v>
+        <v>0.001294812303967774</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0009803923312574625</v>
+        <v>0.0001806562067940831</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0009866204345598817</v>
+        <v>0.001415633945725858</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.002225650008767843</v>
+        <v>0.0009206050308421254</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.000251098332228139</v>
+        <v>0.0002887900627683848</v>
       </c>
       <c r="GG12" t="n">
-        <v>5.014188718632795e-05</v>
+        <v>0.00041184775182046</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01531888358294964</v>
+        <v>0.02166053466498852</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1046344414353371</v>
+        <v>0.1785737872123718</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01063996367156506</v>
+        <v>0.00795261561870575</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03886138275265694</v>
+        <v>0.136412039399147</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008640259504318237</v>
+        <v>0.07170338928699493</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1064198985695839</v>
+        <v>0.09748707711696625</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01852899231016636</v>
+        <v>0.09650704264640808</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05602731928229332</v>
+        <v>0.05937090888619423</v>
       </c>
       <c r="I13" t="n">
-        <v>0.008699929341673851</v>
+        <v>0.0202337522059679</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02581781893968582</v>
+        <v>0.002561666071414948</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1021091863512993</v>
+        <v>0.2626113295555115</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007362666074186563</v>
+        <v>0.01801521889865398</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02583645656704903</v>
+        <v>0.1887511163949966</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03143239766359329</v>
+        <v>0.0938107818365097</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08965516090393066</v>
+        <v>0.154162809252739</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0155055820941925</v>
+        <v>0.1047903075814247</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01956318691372871</v>
+        <v>0.006631497293710709</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02053374424576759</v>
+        <v>0.001024282537400723</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00318602193146944</v>
+        <v>0.00770663283765316</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002751719206571579</v>
+        <v>0.03728143125772476</v>
       </c>
       <c r="U13" t="n">
-        <v>0.005601218435913324</v>
+        <v>0.04609309881925583</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01883573643863201</v>
+        <v>0.1241642832756042</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03469503298401833</v>
+        <v>0.2151554524898529</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01984584890305996</v>
+        <v>0.08967956900596619</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.004787353333085775</v>
+        <v>0.04148048162460327</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02028319239616394</v>
+        <v>0.01450727693736553</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01392728183418512</v>
+        <v>0.05922725796699524</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003972148988395929</v>
+        <v>0.06999461352825165</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.001562053337693214</v>
+        <v>0.02756042778491974</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.006501047406345606</v>
+        <v>0.007900143973529339</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.00861552357673645</v>
+        <v>0.01838042959570885</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01747178100049496</v>
+        <v>0.08309968560934067</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01980971917510033</v>
+        <v>0.114991083741188</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001344195567071438</v>
+        <v>0.04726070910692215</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.008689025416970253</v>
+        <v>0.04195206612348557</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.003932366147637367</v>
+        <v>0.09530384838581085</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01695773750543594</v>
+        <v>0.02844695560634136</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.00424607191234827</v>
+        <v>0.02959871664643288</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003156996797770262</v>
+        <v>0.001583774574100971</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01128431037068367</v>
+        <v>0.07820978760719299</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0009794957004487514</v>
+        <v>0.06008752062916756</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0135558657348156</v>
+        <v>0.03273599594831467</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.006050389260053635</v>
+        <v>0.009148061275482178</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.006062877830117941</v>
+        <v>0.09544059634208679</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.008444678038358688</v>
+        <v>0.0411529578268528</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001600628718733788</v>
+        <v>0.04636445268988609</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05674031004309654</v>
+        <v>0.3673016428947449</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001706946641206741</v>
+        <v>0.04832600057125092</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0205747801810503</v>
+        <v>0.07819843292236328</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.005035593174397945</v>
+        <v>0.01283285766839981</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.05304979160428047</v>
+        <v>0.07608754187822342</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02619048580527306</v>
+        <v>0.08567699790000916</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.009705772623419762</v>
+        <v>0.08169609308242798</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.02099384739995003</v>
+        <v>0.05363263189792633</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.008607165887951851</v>
+        <v>0.03290436044335365</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03988736495375633</v>
+        <v>0.05643189325928688</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.02709124609827995</v>
+        <v>0.04187795519828796</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004587981849908829</v>
+        <v>0.06287360191345215</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0008425358682870865</v>
+        <v>0.05224410444498062</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02432217448949814</v>
+        <v>0.07855284214019775</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.007865592837333679</v>
+        <v>0.155725434422493</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002021066378802061</v>
+        <v>0.01083500869572163</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01449432782828808</v>
+        <v>0.01173003576695919</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01048014499247074</v>
+        <v>0.045137669891119</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02288821712136269</v>
+        <v>0.05282531678676605</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01419212389737368</v>
+        <v>0.001364118419587612</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.007658825721591711</v>
+        <v>0.0623907558619976</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.01026460528373718</v>
+        <v>0.01531382370740175</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.002298495499417186</v>
+        <v>0.009984028525650501</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.005801288411021233</v>
+        <v>0.1468741148710251</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.007560396566987038</v>
+        <v>0.04617383703589439</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.004430596716701984</v>
+        <v>0.02654981799423695</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.001100817229598761</v>
+        <v>0.0303546879440546</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03988118842244148</v>
+        <v>0.175421267747879</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.00715260487049818</v>
+        <v>0.03362005949020386</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.009519140236079693</v>
+        <v>0.1427318304777145</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0009837441612035036</v>
+        <v>0.2069347202777863</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.02748111821711063</v>
+        <v>0.1457012742757797</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.003368345554918051</v>
+        <v>0.02635703980922699</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001382960006594658</v>
+        <v>0.02385006844997406</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01101546920835972</v>
+        <v>0.07582622021436691</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.002713734516873956</v>
+        <v>0.02286163717508316</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01604682020843029</v>
+        <v>0.06250562518835068</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01211367081850767</v>
+        <v>0.002994465408846736</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.002498126588761806</v>
+        <v>0.02971430867910385</v>
       </c>
       <c r="CH13" t="n">
-        <v>8.826097473502159e-05</v>
+        <v>0.006008973345160484</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01805953122675419</v>
+        <v>0.05331974849104881</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.008663628250360489</v>
+        <v>0.04073276370763779</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.009982407093048096</v>
+        <v>0.02565945312380791</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01058194693177938</v>
+        <v>0.01124825421720743</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01460465788841248</v>
+        <v>0.08765799552202225</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01809539087116718</v>
+        <v>0.2030872404575348</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0008826850680634379</v>
+        <v>0.006382664665579796</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.02500171586871147</v>
+        <v>0.01984060555696487</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.926580004394054e-06</v>
+        <v>0.1267546862363815</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.003851587418466806</v>
+        <v>0.1703343987464905</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0214470811188221</v>
+        <v>0.06195510178804398</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01273605599999428</v>
+        <v>0.08451178669929504</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.008697023615241051</v>
+        <v>0.09275184571743011</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001798395998775959</v>
+        <v>0.03353973850607872</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01435009390115738</v>
+        <v>0.05406281724572182</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01020972244441509</v>
+        <v>0.003794851712882519</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.006025565322488546</v>
+        <v>0.01527043059468269</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.002592607866972685</v>
+        <v>0.01097767800092697</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01812541484832764</v>
+        <v>0.02941737696528435</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.008643193170428276</v>
+        <v>0.02356361225247383</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.01456367038190365</v>
+        <v>0.02792511507868767</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.006682754494249821</v>
+        <v>0.003606167621910572</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.002388311084359884</v>
+        <v>0.00870815385133028</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002419710857793689</v>
+        <v>0.04186142981052399</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.001141125569120049</v>
+        <v>0.06459639221429825</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.05665037781000137</v>
+        <v>0.001946087926626205</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01316325832158327</v>
+        <v>0.05932776257395744</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0305376909673214</v>
+        <v>0.07898970693349838</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.007879555225372314</v>
+        <v>0.07808328419923782</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0229729488492012</v>
+        <v>0.009327433072030544</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02292496897280216</v>
+        <v>0.1246466115117073</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.001698239706456661</v>
+        <v>0.02453520148992538</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.006337918341159821</v>
+        <v>0.01212941203266382</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01514085102826357</v>
+        <v>0.001767224632203579</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.005084037780761719</v>
+        <v>0.1685210466384888</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01856083236634731</v>
+        <v>0.03864078968763351</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.008695066906511784</v>
+        <v>0.04834172502160072</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0008573300438001752</v>
+        <v>0.001316264271736145</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001170361880213022</v>
+        <v>0.06962049752473831</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.007322131190448999</v>
+        <v>0.0248836949467659</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002011070027947426</v>
+        <v>0.03569485992193222</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.008587455376982689</v>
+        <v>0.03200694173574448</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.006540410686284304</v>
+        <v>0.03360443562269211</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.00566866947337985</v>
+        <v>0.1009655147790909</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01098582707345486</v>
+        <v>0.04199802502989769</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.02237982489168644</v>
+        <v>0.08248698711395264</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.001179045764729381</v>
+        <v>0.02231928892433643</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.009994729422032833</v>
+        <v>0.04608833789825439</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.02104929834604263</v>
+        <v>0.01880635321140289</v>
       </c>
       <c r="EF13" t="n">
-        <v>1.409417018294334e-05</v>
+        <v>0.03007594496011734</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01783042959868908</v>
+        <v>0.02125947177410126</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.009717829525470734</v>
+        <v>0.004531813785433769</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.008016550913453102</v>
+        <v>0.07519795000553131</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001812103000702336</v>
+        <v>0.04135596007108688</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.007692668586969376</v>
+        <v>0.009167122654616833</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.006241633091121912</v>
+        <v>0.01187595725059509</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.004373446572571993</v>
+        <v>0.005740818567574024</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.006608428899198771</v>
+        <v>0.03596170991659164</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001317248679697514</v>
+        <v>0.01176002807915211</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01049503963440657</v>
+        <v>0.006593411788344383</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004138299264013767</v>
+        <v>0.02229230664670467</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.006750650703907013</v>
+        <v>0.02362911961972713</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.003291316330432892</v>
+        <v>0.03252515569329262</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01964480057358742</v>
+        <v>0.06010475009679794</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01589296571910381</v>
+        <v>0.03187346830964088</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.04330531507730484</v>
+        <v>0.05855660513043404</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.009466586634516716</v>
+        <v>0.0231026466935873</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001582373050041497</v>
+        <v>0.03183114156126976</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01031784620136023</v>
+        <v>0.07346494495868683</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.00635444512590766</v>
+        <v>0.004150476306676865</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001851821783930063</v>
+        <v>0.008043251931667328</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0002365027321502566</v>
+        <v>0.007720788940787315</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.01524699572473764</v>
+        <v>0.04775428026914597</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.01460574567317963</v>
+        <v>0.04419592022895813</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01178315095603466</v>
+        <v>0.02504020556807518</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.009982964023947716</v>
+        <v>0.01207678206264973</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.008130919188261032</v>
+        <v>0.03097677230834961</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.009278120473027229</v>
+        <v>0.08770712465047836</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.00492339301854372</v>
+        <v>0.02399618364870548</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.02115770429372787</v>
+        <v>0.0691417008638382</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0006277215434238315</v>
+        <v>0.0002541444264352322</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.006963528227061033</v>
+        <v>0.08278424292802811</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.008392905816435814</v>
+        <v>0.03017478063702583</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.006776855792850256</v>
+        <v>0.02662731893360615</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.003859392367303371</v>
+        <v>0.003209637477993965</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.004240659065544605</v>
+        <v>0.03462329879403114</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0213893074542284</v>
+        <v>0.2196850627660751</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01348294410854578</v>
+        <v>0.005830243695527315</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.004445722326636314</v>
+        <v>0.1331577003002167</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02977360039949417</v>
+        <v>0.1362886875867844</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02347663603723049</v>
+        <v>0.09004668146371841</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01979248411953449</v>
+        <v>0.1349580734968185</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.01024803891777992</v>
+        <v>0.005720313638448715</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01183501072227955</v>
+        <v>0.07503367215394974</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01599760912358761</v>
+        <v>0.003443799912929535</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01150551624596119</v>
+        <v>0.0005504577420651913</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.008332669734954834</v>
+        <v>0.03787240386009216</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01155486516654491</v>
+        <v>0.01337852329015732</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.006337415426969528</v>
+        <v>0.08632685244083405</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001174187287688255</v>
+        <v>0.04616826772689819</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.03593927621841431</v>
+        <v>0.01839929632842541</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.007220597937703133</v>
+        <v>0.0101117929443717</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.00423735287040472</v>
+        <v>0.0414041168987751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8.517997048329562e-05</v>
+        <v>0.04915778711438179</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002905787201598287</v>
+        <v>0.1263334602117538</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002999835996888578</v>
+        <v>0.01205425895750523</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001349108526483178</v>
+        <v>0.1369883269071579</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0007236249512061477</v>
+        <v>0.002612384501844645</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004158563097007573</v>
+        <v>0.0733996108174324</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002256497391499579</v>
+        <v>0.06148196756839752</v>
       </c>
       <c r="H14" t="n">
-        <v>8.304441871587187e-05</v>
+        <v>0.05318442359566689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001243821607204154</v>
+        <v>0.004198582842946053</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002064517029793933</v>
+        <v>0.02158722095191479</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00216554501093924</v>
+        <v>0.1381260454654694</v>
       </c>
       <c r="L14" t="n">
-        <v>2.910694456659257e-05</v>
+        <v>0.0263739600777626</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001128363539464772</v>
+        <v>0.1787571012973785</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0007950774161145091</v>
+        <v>0.03995107486844063</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0004013832949567586</v>
+        <v>0.08777931332588196</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0002002334513235837</v>
+        <v>0.04550737887620926</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0004976902855560184</v>
+        <v>0.001736707054078579</v>
       </c>
       <c r="R14" t="n">
-        <v>3.156140155624598e-05</v>
+        <v>0.007293693721294403</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001219372570631094</v>
+        <v>0.01345502026379108</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0004304568283259869</v>
+        <v>0.004528521560132504</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001358531881123781</v>
+        <v>0.01570381224155426</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0003659657959360629</v>
+        <v>0.01682991534471512</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0002762566728051752</v>
+        <v>0.02881509624421597</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0002651521936058998</v>
+        <v>0.03406378254294395</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001900075585581362</v>
+        <v>0.02675739116966724</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003301849355921149</v>
+        <v>0.03202143311500549</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001837444433476776</v>
+        <v>0.001550292363390326</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.571205449290574e-05</v>
+        <v>0.0004706354811787605</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.405614840332419e-05</v>
+        <v>0.004709586501121521</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0002160184667445719</v>
+        <v>0.01791871339082718</v>
       </c>
       <c r="AE14" t="n">
-        <v>5.611181040876545e-05</v>
+        <v>0.06478023529052734</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.235739131923765e-05</v>
+        <v>0.02589965611696243</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.450542034348473e-05</v>
+        <v>0.0444563589990139</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.240361936856061e-05</v>
+        <v>0.01294905133545399</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0002639646700117737</v>
+        <v>0.05012865737080574</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5.911779953748919e-05</v>
+        <v>0.02937272191047668</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0003510949318297207</v>
+        <v>0.001834565307945013</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001433662982890382</v>
+        <v>0.03862561658024788</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.812895789043978e-08</v>
+        <v>0.01878848671913147</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002596845151856542</v>
+        <v>0.04329147189855576</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0003287750587332994</v>
+        <v>0.02088052593171597</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0003558089956641197</v>
+        <v>0.03207805752754211</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.809225593926385e-05</v>
+        <v>0.002503473311662674</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0002477050002198666</v>
+        <v>0.01252483110874891</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001444210211047903</v>
+        <v>0.0143036087974906</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.925446460722014e-05</v>
+        <v>0.007889959961175919</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001789478003047407</v>
+        <v>0.09990350902080536</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.322189048863947e-05</v>
+        <v>0.03649189695715904</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0001699198764981702</v>
+        <v>0.04319736361503601</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.027361551881768e-05</v>
+        <v>0.1023806408047676</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.922105704783462e-05</v>
+        <v>0.05762962996959686</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001978773216251284</v>
+        <v>0.001077937195077538</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0003808103210758418</v>
+        <v>0.02159051410853863</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.985868145013228e-06</v>
+        <v>0.02169452421367168</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.052801083773375e-05</v>
+        <v>0.002780606038868427</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0004722712328657508</v>
+        <v>0.03220582008361816</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0006121016922406852</v>
+        <v>0.01660974882543087</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0004195997898932546</v>
+        <v>0.02075871080160141</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0009873473318293691</v>
+        <v>0.08012030273675919</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001864837540779263</v>
+        <v>0.005231353454291821</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.40413314208854e-05</v>
+        <v>0.005292531102895737</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0004291873774491251</v>
+        <v>0.04768779501318932</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.065139652695507e-05</v>
+        <v>0.02750185690820217</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0002562059962656349</v>
+        <v>0.01583926379680634</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0006023970199748874</v>
+        <v>0.01840995997190475</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0002401783131062984</v>
+        <v>0.0119779072701931</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.862978544726502e-05</v>
+        <v>0.01667235046625137</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0003663985698949546</v>
+        <v>0.02707882970571518</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0002517936809454113</v>
+        <v>0.00123961316421628</v>
       </c>
       <c r="BR14" t="n">
-        <v>4.011499549960718e-05</v>
+        <v>0.02389119006693363</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001519975776318461</v>
+        <v>0.0120397862046957</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.079566759988666e-05</v>
+        <v>0.01463928632438183</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001632771891308948</v>
+        <v>0.001116028055548668</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0009845386957749724</v>
+        <v>0.06539323925971985</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.000300965242786333</v>
+        <v>0.016917509958148</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0001211538256029598</v>
+        <v>0.05170747637748718</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.725825293571688e-06</v>
+        <v>0.01968944817781448</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003499117447063327</v>
+        <v>0.04810070618987083</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002432333712931722</v>
+        <v>0.03450293466448784</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.352877971949056e-05</v>
+        <v>0.002203550655394793</v>
       </c>
       <c r="CC14" t="n">
-        <v>6.166450475575402e-05</v>
+        <v>0.01027736999094486</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.106789517914876e-05</v>
+        <v>0.008908845484256744</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0004813903942704201</v>
+        <v>0.03786927089095116</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001699732092674822</v>
+        <v>0.001758090336807072</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001856296294135973</v>
+        <v>0.04146329313516617</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001185333312605508</v>
+        <v>0.01015382446348667</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001003443176159635</v>
+        <v>0.00727888336405158</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001053591113304719</v>
+        <v>0.002221489325165749</v>
       </c>
       <c r="CK14" t="n">
-        <v>6.662821397185326e-05</v>
+        <v>0.01153963897377253</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0001236885145772249</v>
+        <v>0.001821135170757771</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.000569614116102457</v>
+        <v>0.04877109453082085</v>
       </c>
       <c r="CN14" t="n">
-        <v>9.586965461494401e-05</v>
+        <v>0.06331878900527954</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001508389541413635</v>
+        <v>0.05020145699381828</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.000289891439024359</v>
+        <v>0.06381134688854218</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002534148516133428</v>
+        <v>0.008605955168604851</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0006181662320159376</v>
+        <v>0.001577459275722504</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0003112837730441242</v>
+        <v>0.02995827421545982</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0002134239475708455</v>
+        <v>0.01392088923603296</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002669551759026945</v>
+        <v>0.0124124838039279</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.106194031308405e-05</v>
+        <v>0.00480719655752182</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0004340850573498756</v>
+        <v>0.03475832566618919</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0002129210042767227</v>
+        <v>0.004225295968353748</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0002760759962256998</v>
+        <v>0.04962096735835075</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0001091469821403734</v>
+        <v>0.01583594270050526</v>
       </c>
       <c r="DA14" t="n">
-        <v>8.231729589169845e-05</v>
+        <v>0.006357332225888968</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001245816383743659</v>
+        <v>0.003302988829091191</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001426053640898317</v>
+        <v>0.01536301150918007</v>
       </c>
       <c r="DD14" t="n">
-        <v>7.439974433509633e-05</v>
+        <v>0.004945543128997087</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001589764870004728</v>
+        <v>0.01836718991398811</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0008114516385830939</v>
+        <v>0.0110833365470171</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001583108241902664</v>
+        <v>0.007062440272420645</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0007993574836291373</v>
+        <v>0.04653029888868332</v>
       </c>
       <c r="DI14" t="n">
-        <v>1.002826866169926e-05</v>
+        <v>0.006045950576663017</v>
       </c>
       <c r="DJ14" t="n">
-        <v>6.601663335459307e-05</v>
+        <v>0.01355315465480089</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0001886206300696358</v>
+        <v>0.009914033114910126</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0001186056906590238</v>
+        <v>0.073820561170578</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001254496746696532</v>
+        <v>0.01847145333886147</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0002806848497129977</v>
+        <v>0.007392504252493382</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001961523230420426</v>
+        <v>0.03760883212089539</v>
       </c>
       <c r="DP14" t="n">
-        <v>6.301308167167008e-05</v>
+        <v>0.01010929048061371</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001326093333773315</v>
+        <v>0.02915398590266705</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.833688091021031e-05</v>
+        <v>0.02079524658620358</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0001490974245825782</v>
+        <v>0.009991137310862541</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0001499410136602819</v>
+        <v>0.03927401453256607</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001316209963988513</v>
+        <v>0.02422107197344303</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0001033654625643976</v>
+        <v>0.02540428377687931</v>
       </c>
       <c r="DW14" t="n">
-        <v>2.541800677136052e-05</v>
+        <v>0.01724149286746979</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001944883842952549</v>
+        <v>0.02053633518517017</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002106374158756807</v>
+        <v>0.03534822165966034</v>
       </c>
       <c r="DZ14" t="n">
-        <v>9.665842662798241e-05</v>
+        <v>0.02158948220312595</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003151525743305683</v>
+        <v>0.04437801241874695</v>
       </c>
       <c r="EB14" t="n">
-        <v>6.375316297635436e-05</v>
+        <v>0.0100336279720068</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0001962254464160651</v>
+        <v>0.005748966243118048</v>
       </c>
       <c r="ED14" t="n">
-        <v>8.921341213863343e-05</v>
+        <v>0.07379598170518875</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0002186468045692891</v>
+        <v>0.04583068937063217</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0003040994051843882</v>
+        <v>0.003097039880231023</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.000452428765129298</v>
+        <v>0.001233837334439158</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0002617327845655382</v>
+        <v>0.01549268886446953</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001446200622012839</v>
+        <v>0.01976331323385239</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001132178877014667</v>
+        <v>0.02061024866998196</v>
       </c>
       <c r="EK14" t="n">
-        <v>7.3962815804407e-05</v>
+        <v>0.007696536835283041</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.00011469230230432</v>
+        <v>0.006669604685157537</v>
       </c>
       <c r="EM14" t="n">
-        <v>7.984504190972075e-05</v>
+        <v>0.01060240902006626</v>
       </c>
       <c r="EN14" t="n">
-        <v>5.764192246715538e-05</v>
+        <v>0.005290096160024405</v>
       </c>
       <c r="EO14" t="n">
-        <v>6.947004294488579e-05</v>
+        <v>0.009937569499015808</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0002308560942765325</v>
+        <v>0.02720466814935207</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001914648164529353</v>
+        <v>0.002282324014231563</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001938375789904967</v>
+        <v>0.02971602976322174</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0001223708095494658</v>
+        <v>0.02660520747303963</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0001416762097505853</v>
+        <v>0.005110584199428558</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.000298579572699964</v>
+        <v>0.0236875806003809</v>
       </c>
       <c r="EV14" t="n">
-        <v>5.501626219484024e-05</v>
+        <v>0.004687645006924868</v>
       </c>
       <c r="EW14" t="n">
-        <v>8.127887849695981e-05</v>
+        <v>0.02749464102089405</v>
       </c>
       <c r="EX14" t="n">
-        <v>7.676189852645621e-05</v>
+        <v>0.006110735237598419</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0004463049990590662</v>
+        <v>0.03904486447572708</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0001760279119480401</v>
+        <v>0.0006028995267115533</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0002252255217172205</v>
+        <v>0.0512591190636158</v>
       </c>
       <c r="FB14" t="n">
-        <v>4.837551387026906e-05</v>
+        <v>0.006742021068930626</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0001072165177902207</v>
+        <v>0.009847557172179222</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001520679506938905</v>
+        <v>0.007336368784308434</v>
       </c>
       <c r="FE14" t="n">
-        <v>9.657647024141625e-05</v>
+        <v>0.01829423010349274</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001493051822762936</v>
+        <v>0.002092791954055429</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.000169846331118606</v>
+        <v>0.006488427519798279</v>
       </c>
       <c r="FH14" t="n">
-        <v>8.627595525467768e-05</v>
+        <v>0.005576469004154205</v>
       </c>
       <c r="FI14" t="n">
-        <v>8.32560399430804e-05</v>
+        <v>0.0180041491985321</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0003004730679094791</v>
+        <v>0.02541392296552658</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0003141665365546942</v>
+        <v>0.01844678819179535</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.000261552951997146</v>
+        <v>0.01653186418116093</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0001102002133848146</v>
+        <v>0.0120365796610713</v>
       </c>
       <c r="FN14" t="n">
-        <v>8.824211545288563e-05</v>
+        <v>0.008899341337382793</v>
       </c>
       <c r="FO14" t="n">
-        <v>2.36294545175042e-05</v>
+        <v>0.02611492574214935</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0002301581407664344</v>
+        <v>0.05907778814435005</v>
       </c>
       <c r="FQ14" t="n">
-        <v>2.312259857717436e-05</v>
+        <v>0.03121763654053211</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.000632398878224194</v>
+        <v>0.04379907250404358</v>
       </c>
       <c r="FS14" t="n">
-        <v>3.170921991113573e-05</v>
+        <v>0.01925481669604778</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0003253940667491406</v>
+        <v>0.006753457244485617</v>
       </c>
       <c r="FU14" t="n">
-        <v>7.748477219138294e-05</v>
+        <v>0.0004202127456665039</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001259372947970405</v>
+        <v>0.03327376022934914</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001082704256987199</v>
+        <v>0.02911784686148167</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.000319855404086411</v>
+        <v>0.004801858682185411</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0003597519535105675</v>
+        <v>0.005282440222799778</v>
       </c>
       <c r="FZ14" t="n">
-        <v>4.521890514297411e-05</v>
+        <v>0.000332963652908802</v>
       </c>
       <c r="GA14" t="n">
-        <v>4.878289473708719e-05</v>
+        <v>0.02216555178165436</v>
       </c>
       <c r="GB14" t="n">
-        <v>2.813588071148843e-05</v>
+        <v>0.0372207909822464</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001491532020736486</v>
+        <v>4.073604941368103e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0002742159704212099</v>
+        <v>0.02247150987386703</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0005092241335660219</v>
+        <v>0.07250140607357025</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001885541132651269</v>
+        <v>0.00337115116417408</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0002479297399986535</v>
+        <v>0.008777662180364132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.003748457878828049</v>
+        <v>0.1479993611574173</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2939541637897491</v>
+        <v>0.8057808876037598</v>
       </c>
       <c r="C15" t="n">
-        <v>0.07268088310956955</v>
+        <v>0.2616168856620789</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1269596815109253</v>
+        <v>0.1227219253778458</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05578209459781647</v>
+        <v>0.1107669621706009</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02790944650769234</v>
+        <v>0.3133708238601685</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02080770209431648</v>
+        <v>0.1412106603384018</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04571329057216644</v>
+        <v>0.2053775638341904</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003620733739808202</v>
+        <v>0.05273803323507309</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09061772376298904</v>
+        <v>0.1778853833675385</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2642996311187744</v>
+        <v>0.8466284275054932</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07237890362739563</v>
+        <v>0.2755619287490845</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1635575741529465</v>
+        <v>0.2471258938312531</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01880484446883202</v>
+        <v>0.2757535874843597</v>
       </c>
       <c r="O15" t="n">
-        <v>0.03038492798805237</v>
+        <v>0.0635087862610817</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06836849451065063</v>
+        <v>0.1182325333356857</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09692665934562683</v>
+        <v>0.229546919465065</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05150145292282104</v>
+        <v>0.01818243786692619</v>
       </c>
       <c r="S15" t="n">
-        <v>0.006960033439099789</v>
+        <v>0.04138768091797829</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04832576587796211</v>
+        <v>0.05963390320539474</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06474906206130981</v>
+        <v>0.01121669635176659</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04914366826415062</v>
+        <v>0.0427234023809433</v>
       </c>
       <c r="W15" t="n">
-        <v>0.005010166671127081</v>
+        <v>0.06075870245695114</v>
       </c>
       <c r="X15" t="n">
-        <v>0.006536731030791998</v>
+        <v>0.03529643267393112</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.00378851592540741</v>
+        <v>0.02707856148481369</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01423497498035431</v>
+        <v>0.05141932517290115</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02261601015925407</v>
+        <v>0.1526788324117661</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06047169864177704</v>
+        <v>0.1061649471521378</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03549952059984207</v>
+        <v>0.06009778007864952</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0464777797460556</v>
+        <v>0.139738529920578</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.02117948606610298</v>
+        <v>0.1796897649765015</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.008490766398608685</v>
+        <v>0.03412321954965591</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001585403457283974</v>
+        <v>0.05570247024297714</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.006654020864516497</v>
+        <v>0.08557349443435669</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.00161316804587841</v>
+        <v>0.03570729494094849</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02668445557355881</v>
+        <v>0.07351884245872498</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.04839631915092468</v>
+        <v>0.04063788056373596</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03317709639668465</v>
+        <v>0.3046488165855408</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.01829063892364502</v>
+        <v>0.1068061292171478</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03750894591212273</v>
+        <v>0.0007556525524705648</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02918210066854954</v>
+        <v>0.2425719201564789</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.04211440682411194</v>
+        <v>0.02869201451539993</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.01913498528301716</v>
+        <v>0.04450880736112595</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.04617326334118843</v>
+        <v>0.003776452504098415</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.02386298216879368</v>
+        <v>0.03830906003713608</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.06975215673446655</v>
+        <v>0.02359763532876968</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1507366150617599</v>
+        <v>0.4175817370414734</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.01644027046859264</v>
+        <v>0.03052296116948128</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.03041206300258636</v>
+        <v>0.02870229631662369</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0006745709106326103</v>
+        <v>0.1532394587993622</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01734867133200169</v>
+        <v>0.08404919505119324</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.009404949843883514</v>
+        <v>0.02136016450822353</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.02819161489605904</v>
+        <v>0.0230996161699295</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0522523857653141</v>
+        <v>0.006145630031824112</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.06212611868977547</v>
+        <v>0.1344186216592789</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.07478228211402893</v>
+        <v>0.01241917908191681</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.05847933143377304</v>
+        <v>0.1758820116519928</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.02870714105665684</v>
+        <v>0.08675403147935867</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1320097595453262</v>
+        <v>0.150426909327507</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.05194186046719551</v>
+        <v>0.09744701534509659</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.02403495088219643</v>
+        <v>0.007826268672943115</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1484038978815079</v>
+        <v>0.01830331049859524</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.01743110083043575</v>
+        <v>0.08853492885828018</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.03117542713880539</v>
+        <v>0.05826643109321594</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.01459899544715881</v>
+        <v>0.1255705058574677</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.02659819088876247</v>
+        <v>0.01292608119547367</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.02982909604907036</v>
+        <v>0.08437532931566238</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05530661717057228</v>
+        <v>0.05693521723151207</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.03587349131703377</v>
+        <v>0.007170009426772594</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.03614123910665512</v>
+        <v>0.07552987337112427</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.02578970976173878</v>
+        <v>0.06614759564399719</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.03956435993313789</v>
+        <v>0.06456413120031357</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.07947606593370438</v>
+        <v>0.04989799857139587</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0850117951631546</v>
+        <v>0.3532798290252686</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.02994279935956001</v>
+        <v>0.04796205461025238</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0372588112950325</v>
+        <v>0.07364462316036224</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08128539472818375</v>
+        <v>0.008183723315596581</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01924659311771393</v>
+        <v>0.07297418266534805</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.01547825150191784</v>
+        <v>0.04047926142811775</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0244742501527071</v>
+        <v>0.02249196730554104</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.07120814919471741</v>
+        <v>0.08321507275104523</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0352015309035778</v>
+        <v>0.05624024197459221</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0494392067193985</v>
+        <v>0.262098103761673</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.01021013222634792</v>
+        <v>0.06913086771965027</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02990307845175266</v>
+        <v>0.02675773575901985</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05015784129500389</v>
+        <v>0.001374906860291958</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0245997104793787</v>
+        <v>0.09942124783992767</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.008879158645868301</v>
+        <v>0.01200476940721273</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0153520992025733</v>
+        <v>0.05112218111753464</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.02293953858315945</v>
+        <v>0.02108322829008102</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0005823196843266487</v>
+        <v>0.05170990526676178</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.01858789287507534</v>
+        <v>0.1863511651754379</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.008280316367745399</v>
+        <v>0.1079643666744232</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0187825970351696</v>
+        <v>0.1055620610713959</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.06248272210359573</v>
+        <v>0.1980611532926559</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.01726715639233589</v>
+        <v>0.04246694594621658</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.04085820540785789</v>
+        <v>0.08635079860687256</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0685279592871666</v>
+        <v>0.1216582357883453</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.02463406510651112</v>
+        <v>0.01780746504664421</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.03046001866459846</v>
+        <v>0.04428992792963982</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.04685439914464951</v>
+        <v>0.244955763220787</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.003732652170583606</v>
+        <v>0.05870847776532173</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03090731613337994</v>
+        <v>0.04305195435881615</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0351288765668869</v>
+        <v>0.02014775760471821</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.02755447290837765</v>
+        <v>0.09639044106006622</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.01616587117314339</v>
+        <v>0.01682654768228531</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.003163305809721351</v>
+        <v>0.05827955156564713</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.02039527706801891</v>
+        <v>0.008511066436767578</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.04656404256820679</v>
+        <v>0.01175422314554453</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.2041345089673996</v>
+        <v>0.1486823260784149</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.01512525975704193</v>
+        <v>0.1468397676944733</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.06905469298362732</v>
+        <v>0.03530516475439072</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.001180378487333655</v>
+        <v>0.06191288679838181</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.09464193880558014</v>
+        <v>0.4125090837478638</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.07505388557910919</v>
+        <v>0.04977539926767349</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.001306222751736641</v>
+        <v>0.02720612660050392</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.03368007019162178</v>
+        <v>0.06496924161911011</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.07282645255327225</v>
+        <v>0.06341788172721863</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03610574081540108</v>
+        <v>0.1713798046112061</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1140890121459961</v>
+        <v>0.01873312145471573</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.07032424956560135</v>
+        <v>0.008442810736596584</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.07825019955635071</v>
+        <v>0.02544073387980461</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.04568967968225479</v>
+        <v>0.1024235710501671</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.01328903064131737</v>
+        <v>0.0002816212363541126</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.03179099410772324</v>
+        <v>0.06924431025981903</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.005958736408501863</v>
+        <v>0.1289355307817459</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0377022847533226</v>
+        <v>0.05535101890563965</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.008282125927507877</v>
+        <v>0.0300101712346077</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.04294783249497414</v>
+        <v>0.1090410649776459</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.05100108683109283</v>
+        <v>0.02909762412309647</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03240480273962021</v>
+        <v>0.007128998637199402</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.1004563197493553</v>
+        <v>0.2577491402626038</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.005629746243357658</v>
+        <v>0.03733990713953972</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.04015978053212166</v>
+        <v>0.0841609314084053</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.01004400104284286</v>
+        <v>0.07650899142026901</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.05901101976633072</v>
+        <v>0.01806469261646271</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.04402438551187515</v>
+        <v>0.2270160168409348</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.006809934042394161</v>
+        <v>0.05715751275420189</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.009555567987263203</v>
+        <v>0.02722520008683205</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01825164072215557</v>
+        <v>0.05062229931354523</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.002297178376466036</v>
+        <v>0.09206567704677582</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.004097925964742899</v>
+        <v>0.01402739249169827</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.02441642619669437</v>
+        <v>0.06213074177503586</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.02920850925147533</v>
+        <v>0.06763466447591782</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.007343227509409189</v>
+        <v>0.02682765200734138</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04243363812565804</v>
+        <v>0.2189231514930725</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.01995217241346836</v>
+        <v>0.02173428796231747</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.002177890855818987</v>
+        <v>0.06844388693571091</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02873652614653111</v>
+        <v>0.0717683732509613</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.04690307006239891</v>
+        <v>0.04018166288733482</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0581616684794426</v>
+        <v>0.05548195540904999</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.08005588501691818</v>
+        <v>0.1359802782535553</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.03173582628369331</v>
+        <v>0.01235565077513456</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.02597500942647457</v>
+        <v>0.05999510362744331</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.06529874354600906</v>
+        <v>0.2902953028678894</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001393980230204761</v>
+        <v>0.06861221045255661</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.03302001953125</v>
+        <v>0.02743261307477951</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02887941524386406</v>
+        <v>0.00758734717965126</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01701273769140244</v>
+        <v>0.08932438492774963</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.03131158649921417</v>
+        <v>0.009473246522247791</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.006384379230439663</v>
+        <v>0.06803949177265167</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.03067784756422043</v>
+        <v>0.01773908361792564</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.008677053265273571</v>
+        <v>0.01353362388908863</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0282707791775465</v>
+        <v>0.09368924796581268</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.02899776585400105</v>
+        <v>0.06427460163831711</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.01544584706425667</v>
+        <v>0.01163276843726635</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.03826893121004105</v>
+        <v>0.06712596863508224</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.03465059772133827</v>
+        <v>0.04173639416694641</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.01393864024430513</v>
+        <v>0.004216802772134542</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.01118767634034157</v>
+        <v>0.03966108709573746</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.01385708898305893</v>
+        <v>0.1402339786291122</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.1139800697565079</v>
+        <v>0.08793985843658447</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.05684257298707962</v>
+        <v>0.1917188763618469</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.1888675540685654</v>
+        <v>0.1331992298364639</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.03264882415533066</v>
+        <v>0.1768406927585602</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.06777483224868774</v>
+        <v>0.1079248189926147</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.02821586281061172</v>
+        <v>0.1476075500249863</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.01513562444597483</v>
+        <v>0.1410698294639587</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.004907233640551567</v>
+        <v>0.1309040039777756</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.05558520182967186</v>
+        <v>0.08231263607740402</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.02584340795874596</v>
+        <v>0.07936416566371918</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02230169996619225</v>
+        <v>0.1472255438566208</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.004494910594075918</v>
+        <v>0.00661032646894455</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.006736270152032375</v>
+        <v>0.02358419634401798</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.05161187052726746</v>
+        <v>0.05357491225004196</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0649915412068367</v>
+        <v>0.08185164630413055</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.06732350587844849</v>
+        <v>0.02499476075172424</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0085792550817132</v>
+        <v>0.1054015755653381</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.01701649278402328</v>
+        <v>0.04409805312752724</v>
       </c>
     </row>
   </sheetData>
